--- a/research/traditional_assets/database/data/australia/australia_trucking.xlsx
+++ b/research/traditional_assets/database/data/australia/australia_trucking.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08164401643118133</v>
+        <v>0.08143058438188779</v>
       </c>
       <c r="C2">
-        <v>287.0042324198269</v>
+        <v>284.7526933592654</v>
       </c>
       <c r="D2">
-        <v>256.6042324198269</v>
+        <v>257.7056933592655</v>
       </c>
       <c r="E2">
-        <v>-164.8</v>
+        <v>-161.447</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.353</v>
       </c>
       <c r="G2">
         <v>30.4</v>
@@ -1457,28 +1457,28 @@
         <v>17.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1686559</v>
       </c>
       <c r="N2">
-        <v>17.5</v>
+        <v>17.3313441</v>
       </c>
       <c r="O2">
-        <v>5.25</v>
+        <v>5.19940323</v>
       </c>
       <c r="P2">
-        <v>12.25</v>
+        <v>12.13194087</v>
       </c>
       <c r="Q2">
-        <v>49.25</v>
+        <v>49.13194087</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08164401643118133</v>
+        <v>0.08189745897160383</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919477</v>
+        <v>0.833659560545123</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.761564226333</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08143058438188779</v>
+        <v>0.08121715233259424</v>
       </c>
       <c r="C3">
-        <v>284.7526933592654</v>
+        <v>282.5106509956993</v>
       </c>
       <c r="D3">
-        <v>257.7056933592655</v>
+        <v>258.8166509956994</v>
       </c>
       <c r="E3">
-        <v>-161.447</v>
+        <v>-158.094</v>
       </c>
       <c r="F3">
-        <v>3.353</v>
+        <v>6.706</v>
       </c>
       <c r="G3">
         <v>30.4</v>
@@ -1539,28 +1539,28 @@
         <v>17.5</v>
       </c>
       <c r="M3">
-        <v>0.1686559</v>
+        <v>0.3373118</v>
       </c>
       <c r="N3">
-        <v>17.3313441</v>
+        <v>17.1626882</v>
       </c>
       <c r="O3">
-        <v>5.19940323</v>
+        <v>5.14880646</v>
       </c>
       <c r="P3">
-        <v>12.13194087</v>
+        <v>12.01388174</v>
       </c>
       <c r="Q3">
-        <v>49.13194087</v>
+        <v>49.01388174</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08189745897160383</v>
+        <v>0.08215607380876963</v>
       </c>
       <c r="T3">
-        <v>0.833659560545123</v>
+        <v>0.8396321895789756</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.761564226333</v>
+        <v>51.88078211316652</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08121715233259424</v>
+        <v>0.0810037202833007</v>
       </c>
       <c r="C4">
-        <v>282.5106509956993</v>
+        <v>280.2782286803893</v>
       </c>
       <c r="D4">
-        <v>258.8166509956994</v>
+        <v>259.9372286803894</v>
       </c>
       <c r="E4">
-        <v>-158.094</v>
+        <v>-154.741</v>
       </c>
       <c r="F4">
-        <v>6.706</v>
+        <v>10.059</v>
       </c>
       <c r="G4">
         <v>30.4</v>
@@ -1621,28 +1621,28 @@
         <v>17.5</v>
       </c>
       <c r="M4">
-        <v>0.3373118</v>
+        <v>0.5059676999999999</v>
       </c>
       <c r="N4">
-        <v>17.1626882</v>
+        <v>16.9940323</v>
       </c>
       <c r="O4">
-        <v>5.14880646</v>
+        <v>5.09820969</v>
       </c>
       <c r="P4">
-        <v>12.01388174</v>
+        <v>11.89582261</v>
       </c>
       <c r="Q4">
-        <v>49.01388174</v>
+        <v>48.89582261</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08215607380876963</v>
+        <v>0.08242002091061928</v>
       </c>
       <c r="T4">
-        <v>0.8396321895789756</v>
+        <v>0.8457279656032166</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.88078211316652</v>
+        <v>34.58718807544435</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0810037202833007</v>
+        <v>0.08079028823400715</v>
       </c>
       <c r="C5">
-        <v>280.2782286803893</v>
+        <v>278.0555519101417</v>
       </c>
       <c r="D5">
-        <v>259.9372286803894</v>
+        <v>261.0675519101417</v>
       </c>
       <c r="E5">
-        <v>-154.741</v>
+        <v>-151.388</v>
       </c>
       <c r="F5">
-        <v>10.059</v>
+        <v>13.412</v>
       </c>
       <c r="G5">
         <v>30.4</v>
@@ -1703,28 +1703,28 @@
         <v>17.5</v>
       </c>
       <c r="M5">
-        <v>0.5059676999999999</v>
+        <v>0.6746236</v>
       </c>
       <c r="N5">
-        <v>16.9940323</v>
+        <v>16.8253764</v>
       </c>
       <c r="O5">
-        <v>5.09820969</v>
+        <v>5.04761292</v>
       </c>
       <c r="P5">
-        <v>11.89582261</v>
+        <v>11.77776348</v>
       </c>
       <c r="Q5">
-        <v>48.89582261</v>
+        <v>48.77776348</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08242002091061928</v>
+        <v>0.08268946691042411</v>
       </c>
       <c r="T5">
-        <v>0.8457279656032166</v>
+        <v>0.8519507369612961</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.58718807544435</v>
+        <v>25.94039105658326</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08079028823400715</v>
+        <v>0.08057685618471361</v>
       </c>
       <c r="C6">
-        <v>278.0555519101417</v>
+        <v>275.8427483741611</v>
       </c>
       <c r="D6">
-        <v>261.0675519101417</v>
+        <v>262.2077483741611</v>
       </c>
       <c r="E6">
-        <v>-151.388</v>
+        <v>-148.035</v>
       </c>
       <c r="F6">
-        <v>13.412</v>
+        <v>16.765</v>
       </c>
       <c r="G6">
         <v>30.4</v>
@@ -1785,28 +1785,28 @@
         <v>17.5</v>
       </c>
       <c r="M6">
-        <v>0.6746236</v>
+        <v>0.8432795</v>
       </c>
       <c r="N6">
-        <v>16.8253764</v>
+        <v>16.6567205</v>
       </c>
       <c r="O6">
-        <v>5.04761292</v>
+        <v>4.997016149999999</v>
       </c>
       <c r="P6">
-        <v>11.77776348</v>
+        <v>11.65970435</v>
       </c>
       <c r="Q6">
-        <v>48.77776348</v>
+        <v>48.65970435</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08268946691042411</v>
+        <v>0.08296458545759328</v>
       </c>
       <c r="T6">
-        <v>0.8519507369612961</v>
+        <v>0.8583045140321773</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.94039105658326</v>
+        <v>20.75231284526661</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08057685618471361</v>
+        <v>0.08036342413542007</v>
       </c>
       <c r="C7">
-        <v>275.8427483741611</v>
+        <v>273.6399480021362</v>
       </c>
       <c r="D7">
-        <v>262.2077483741611</v>
+        <v>263.3579480021363</v>
       </c>
       <c r="E7">
-        <v>-148.035</v>
+        <v>-144.682</v>
       </c>
       <c r="F7">
-        <v>16.765</v>
+        <v>20.118</v>
       </c>
       <c r="G7">
         <v>30.4</v>
@@ -1867,28 +1867,28 @@
         <v>17.5</v>
       </c>
       <c r="M7">
-        <v>0.8432795</v>
+        <v>1.0119354</v>
       </c>
       <c r="N7">
-        <v>16.6567205</v>
+        <v>16.4880646</v>
       </c>
       <c r="O7">
-        <v>4.997016149999999</v>
+        <v>4.94641938</v>
       </c>
       <c r="P7">
-        <v>11.65970435</v>
+        <v>11.54164522</v>
       </c>
       <c r="Q7">
-        <v>48.65970435</v>
+        <v>48.54164522</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08296458545759328</v>
+        <v>0.0832455575908724</v>
       </c>
       <c r="T7">
-        <v>0.8583045140321773</v>
+        <v>0.8647934778492474</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.75231284526661</v>
+        <v>17.29359403772217</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08036342413542007</v>
+        <v>0.08014999208612654</v>
       </c>
       <c r="C8">
-        <v>273.6399480021362</v>
+        <v>271.447283013597</v>
       </c>
       <c r="D8">
-        <v>263.3579480021363</v>
+        <v>264.5182830135971</v>
       </c>
       <c r="E8">
-        <v>-144.682</v>
+        <v>-141.329</v>
       </c>
       <c r="F8">
-        <v>20.118</v>
+        <v>23.471</v>
       </c>
       <c r="G8">
         <v>30.4</v>
@@ -1949,28 +1949,28 @@
         <v>17.5</v>
       </c>
       <c r="M8">
-        <v>1.0119354</v>
+        <v>1.1805913</v>
       </c>
       <c r="N8">
-        <v>16.4880646</v>
+        <v>16.3194087</v>
       </c>
       <c r="O8">
-        <v>4.94641938</v>
+        <v>4.89582261</v>
       </c>
       <c r="P8">
-        <v>11.54164522</v>
+        <v>11.42358609</v>
       </c>
       <c r="Q8">
-        <v>48.54164522</v>
+        <v>48.42358609</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0832455575908724</v>
+        <v>0.08353257213561993</v>
       </c>
       <c r="T8">
-        <v>0.8647934778492474</v>
+        <v>0.8714219892752869</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.29359403772218</v>
+        <v>14.82308060376186</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08014999208612653</v>
+        <v>0.07993656003683298</v>
       </c>
       <c r="C9">
-        <v>271.4472830135971</v>
+        <v>269.2648879685824</v>
       </c>
       <c r="D9">
-        <v>264.5182830135971</v>
+        <v>265.6888879685824</v>
       </c>
       <c r="E9">
-        <v>-141.329</v>
+        <v>-137.976</v>
       </c>
       <c r="F9">
-        <v>23.471</v>
+        <v>26.824</v>
       </c>
       <c r="G9">
         <v>30.4</v>
@@ -2031,28 +2031,28 @@
         <v>17.5</v>
       </c>
       <c r="M9">
-        <v>1.1805913</v>
+        <v>1.3492472</v>
       </c>
       <c r="N9">
-        <v>16.3194087</v>
+        <v>16.1507528</v>
       </c>
       <c r="O9">
-        <v>4.89582261</v>
+        <v>4.845225839999999</v>
       </c>
       <c r="P9">
-        <v>11.42358609</v>
+        <v>11.30552696</v>
       </c>
       <c r="Q9">
-        <v>48.42358609</v>
+        <v>48.30552696</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08353257213561993</v>
+        <v>0.08382582612699238</v>
       </c>
       <c r="T9">
-        <v>0.8714219892752869</v>
+        <v>0.8781945987758055</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.82308060376186</v>
+        <v>12.97019552829163</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07993656003683298</v>
+        <v>0.07981762798753943</v>
       </c>
       <c r="C10">
-        <v>269.2648879685824</v>
+        <v>266.568697757824</v>
       </c>
       <c r="D10">
-        <v>265.6888879685824</v>
+        <v>266.345697757824</v>
       </c>
       <c r="E10">
-        <v>-137.976</v>
+        <v>-134.623</v>
       </c>
       <c r="F10">
-        <v>26.824</v>
+        <v>30.177</v>
       </c>
       <c r="G10">
         <v>30.4</v>
@@ -2113,45 +2113,45 @@
         <v>17.5</v>
       </c>
       <c r="M10">
-        <v>1.3492472</v>
+        <v>1.5631686</v>
       </c>
       <c r="N10">
-        <v>16.1507528</v>
+        <v>15.9368314</v>
       </c>
       <c r="O10">
-        <v>4.845225839999999</v>
+        <v>4.78104942</v>
       </c>
       <c r="P10">
-        <v>11.30552696</v>
+        <v>11.15578198</v>
       </c>
       <c r="Q10">
-        <v>48.30552696</v>
+        <v>48.15578198</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08382582612699238</v>
+        <v>0.08412552526103234</v>
       </c>
       <c r="T10">
-        <v>0.8781945987758055</v>
+        <v>0.8851160568367749</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>12.97019552829163</v>
+        <v>11.19520952506339</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07981762798753943</v>
+        <v>0.0796146959382459</v>
       </c>
       <c r="C11">
-        <v>266.568697757824</v>
+        <v>264.3439323922541</v>
       </c>
       <c r="D11">
-        <v>266.345697757824</v>
+        <v>267.4739323922542</v>
       </c>
       <c r="E11">
-        <v>-134.623</v>
+        <v>-131.27</v>
       </c>
       <c r="F11">
-        <v>30.177</v>
+        <v>33.53</v>
       </c>
       <c r="G11">
         <v>30.4</v>
@@ -2195,28 +2195,28 @@
         <v>17.5</v>
       </c>
       <c r="M11">
-        <v>1.5631686</v>
+        <v>1.736854</v>
       </c>
       <c r="N11">
-        <v>15.9368314</v>
+        <v>15.763146</v>
       </c>
       <c r="O11">
-        <v>4.78104942</v>
+        <v>4.7289438</v>
       </c>
       <c r="P11">
-        <v>11.15578198</v>
+        <v>11.0342022</v>
       </c>
       <c r="Q11">
-        <v>48.15578198</v>
+        <v>48.0342022</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08412552526103234</v>
+        <v>0.08443188437582877</v>
       </c>
       <c r="T11">
-        <v>0.8851160568367749</v>
+        <v>0.8921913250768769</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.19520952506339</v>
+        <v>10.07568857255705</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0796146959382459</v>
+        <v>0.07954266388895234</v>
       </c>
       <c r="C12">
-        <v>264.3439323922541</v>
+        <v>261.3937086152511</v>
       </c>
       <c r="D12">
-        <v>267.4739323922542</v>
+        <v>267.8767086152511</v>
       </c>
       <c r="E12">
-        <v>-131.27</v>
+        <v>-127.917</v>
       </c>
       <c r="F12">
-        <v>33.53</v>
+        <v>36.883</v>
       </c>
       <c r="G12">
         <v>30.4</v>
@@ -2277,45 +2277,45 @@
         <v>17.5</v>
       </c>
       <c r="M12">
-        <v>1.736854</v>
+        <v>1.9732405</v>
       </c>
       <c r="N12">
-        <v>15.763146</v>
+        <v>15.5267595</v>
       </c>
       <c r="O12">
-        <v>4.7289438</v>
+        <v>4.65802785</v>
       </c>
       <c r="P12">
-        <v>11.0342022</v>
+        <v>10.86873165</v>
       </c>
       <c r="Q12">
-        <v>48.0342022</v>
+        <v>47.86873165</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08443188437582877</v>
+        <v>0.08474512796511499</v>
       </c>
       <c r="T12">
-        <v>0.8921913250768769</v>
+        <v>0.8994255881088915</v>
       </c>
       <c r="U12">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>10.07568857255705</v>
+        <v>8.868660459786833</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07954266388895234</v>
+        <v>0.07935163183965882</v>
       </c>
       <c r="C13">
-        <v>261.3937086152511</v>
+        <v>259.1147861783193</v>
       </c>
       <c r="D13">
-        <v>267.8767086152511</v>
+        <v>268.9507861783193</v>
       </c>
       <c r="E13">
-        <v>-127.917</v>
+        <v>-124.564</v>
       </c>
       <c r="F13">
-        <v>36.883</v>
+        <v>40.236</v>
       </c>
       <c r="G13">
         <v>30.4</v>
@@ -2359,28 +2359,28 @@
         <v>17.5</v>
       </c>
       <c r="M13">
-        <v>1.9732405</v>
+        <v>2.152626</v>
       </c>
       <c r="N13">
-        <v>15.5267595</v>
+        <v>15.347374</v>
       </c>
       <c r="O13">
-        <v>4.65802785</v>
+        <v>4.6042122</v>
       </c>
       <c r="P13">
-        <v>10.86873165</v>
+        <v>10.7431618</v>
       </c>
       <c r="Q13">
-        <v>47.86873165</v>
+        <v>47.7431618</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08474512796511499</v>
+        <v>0.08506549072688502</v>
       </c>
       <c r="T13">
-        <v>0.8994255881088915</v>
+        <v>0.9068242662098155</v>
       </c>
       <c r="U13">
         <v>0.0535</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.868660459786833</v>
+        <v>8.129605421471265</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07935163183965882</v>
+        <v>0.07923339979036526</v>
       </c>
       <c r="C14">
-        <v>259.1147861783193</v>
+        <v>256.4308716047684</v>
       </c>
       <c r="D14">
-        <v>268.9507861783193</v>
+        <v>269.6198716047684</v>
       </c>
       <c r="E14">
-        <v>-124.564</v>
+        <v>-121.211</v>
       </c>
       <c r="F14">
-        <v>40.236</v>
+        <v>43.58900000000001</v>
       </c>
       <c r="G14">
         <v>30.4</v>
@@ -2441,45 +2441,45 @@
         <v>17.5</v>
       </c>
       <c r="M14">
-        <v>2.152626</v>
+        <v>2.366882700000001</v>
       </c>
       <c r="N14">
-        <v>15.347374</v>
+        <v>15.1331173</v>
       </c>
       <c r="O14">
-        <v>4.6042122</v>
+        <v>4.53993519</v>
       </c>
       <c r="P14">
-        <v>10.7431618</v>
+        <v>10.59318211</v>
       </c>
       <c r="Q14">
-        <v>47.7431618</v>
+        <v>47.59318211</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08506549072688502</v>
+        <v>0.08539321814984513</v>
       </c>
       <c r="T14">
-        <v>0.9068242662098155</v>
+        <v>0.9143930288647836</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>8.129605421471265</v>
+        <v>7.393691288545899</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07923339979036526</v>
+        <v>0.07904796774107171</v>
       </c>
       <c r="C15">
-        <v>256.4308716047684</v>
+        <v>254.1339789160696</v>
       </c>
       <c r="D15">
-        <v>269.6198716047684</v>
+        <v>270.6759789160696</v>
       </c>
       <c r="E15">
-        <v>-121.211</v>
+        <v>-117.858</v>
       </c>
       <c r="F15">
-        <v>43.58900000000001</v>
+        <v>46.94200000000001</v>
       </c>
       <c r="G15">
         <v>30.4</v>
@@ -2523,28 +2523,28 @@
         <v>17.5</v>
       </c>
       <c r="M15">
-        <v>2.366882700000001</v>
+        <v>2.5489506</v>
       </c>
       <c r="N15">
-        <v>15.1331173</v>
+        <v>14.9510494</v>
       </c>
       <c r="O15">
-        <v>4.53993519</v>
+        <v>4.485314819999999</v>
       </c>
       <c r="P15">
-        <v>10.59318211</v>
+        <v>10.46573458</v>
       </c>
       <c r="Q15">
-        <v>47.59318211</v>
+        <v>47.46573458</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08539321814984513</v>
+        <v>0.08572856714078106</v>
       </c>
       <c r="T15">
-        <v>0.9143930288647836</v>
+        <v>0.9221378092559138</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.393691288545899</v>
+        <v>6.865570482221192</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07904796774107171</v>
+        <v>0.07886253569177817</v>
       </c>
       <c r="C16">
-        <v>254.1339789160696</v>
+        <v>251.8453923565011</v>
       </c>
       <c r="D16">
-        <v>270.6759789160696</v>
+        <v>271.7403923565012</v>
       </c>
       <c r="E16">
-        <v>-117.858</v>
+        <v>-114.505</v>
       </c>
       <c r="F16">
-        <v>46.94200000000001</v>
+        <v>50.29500000000001</v>
       </c>
       <c r="G16">
         <v>30.4</v>
@@ -2605,28 +2605,28 @@
         <v>17.5</v>
       </c>
       <c r="M16">
-        <v>2.5489506</v>
+        <v>2.731018500000001</v>
       </c>
       <c r="N16">
-        <v>14.9510494</v>
+        <v>14.7689815</v>
       </c>
       <c r="O16">
-        <v>4.485314819999999</v>
+        <v>4.43069445</v>
       </c>
       <c r="P16">
-        <v>10.46573458</v>
+        <v>10.33828705</v>
       </c>
       <c r="Q16">
-        <v>47.46573458</v>
+        <v>47.33828705</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08572856714078106</v>
+        <v>0.08607180669620962</v>
       </c>
       <c r="T16">
-        <v>0.9221378092559138</v>
+        <v>0.9300648197738942</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.865570482221192</v>
+        <v>6.407865783406446</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07886253569177817</v>
+        <v>0.07878910364248462</v>
       </c>
       <c r="C17">
-        <v>251.8453923565011</v>
+        <v>248.9162231618364</v>
       </c>
       <c r="D17">
-        <v>271.7403923565012</v>
+        <v>272.1642231618364</v>
       </c>
       <c r="E17">
-        <v>-114.505</v>
+        <v>-111.152</v>
       </c>
       <c r="F17">
-        <v>50.295</v>
+        <v>53.648</v>
       </c>
       <c r="G17">
         <v>30.4</v>
@@ -2687,45 +2687,45 @@
         <v>17.5</v>
       </c>
       <c r="M17">
-        <v>2.7310185</v>
+        <v>2.9667344</v>
       </c>
       <c r="N17">
-        <v>14.7689815</v>
+        <v>14.5332656</v>
       </c>
       <c r="O17">
-        <v>4.43069445</v>
+        <v>4.359979679999999</v>
       </c>
       <c r="P17">
-        <v>10.33828705</v>
+        <v>10.17328592</v>
       </c>
       <c r="Q17">
-        <v>47.33828705</v>
+        <v>47.17328592</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08607180669620962</v>
+        <v>0.08642321862200551</v>
       </c>
       <c r="T17">
-        <v>0.9300648197738942</v>
+        <v>0.9381805686375407</v>
       </c>
       <c r="U17">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.407865783406447</v>
+        <v>5.898741727604601</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07878910364248462</v>
+        <v>0.07861067159319109</v>
       </c>
       <c r="C18">
-        <v>248.9162231618364</v>
+        <v>246.5986171109343</v>
       </c>
       <c r="D18">
-        <v>272.1642231618364</v>
+        <v>273.1996171109343</v>
       </c>
       <c r="E18">
-        <v>-111.152</v>
+        <v>-107.799</v>
       </c>
       <c r="F18">
-        <v>53.648</v>
+        <v>57.001</v>
       </c>
       <c r="G18">
         <v>30.4</v>
@@ -2769,28 +2769,28 @@
         <v>17.5</v>
       </c>
       <c r="M18">
-        <v>2.9667344</v>
+        <v>3.1521553</v>
       </c>
       <c r="N18">
-        <v>14.5332656</v>
+        <v>14.3478447</v>
       </c>
       <c r="O18">
-        <v>4.359979679999999</v>
+        <v>4.30435341</v>
       </c>
       <c r="P18">
-        <v>10.17328592</v>
+        <v>10.04349129</v>
       </c>
       <c r="Q18">
-        <v>47.17328592</v>
+        <v>47.04349129</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08642321862200551</v>
+        <v>0.08678309830504952</v>
       </c>
       <c r="T18">
-        <v>0.9381805686375407</v>
+        <v>0.9464918777147693</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.898741727604601</v>
+        <v>5.551756920098447</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07861067159319109</v>
+        <v>0.07843223954389754</v>
       </c>
       <c r="C19">
-        <v>246.5986171109343</v>
+        <v>244.2889190396664</v>
       </c>
       <c r="D19">
-        <v>273.1996171109343</v>
+        <v>274.2429190396664</v>
       </c>
       <c r="E19">
-        <v>-107.799</v>
+        <v>-104.446</v>
       </c>
       <c r="F19">
-        <v>57.001</v>
+        <v>60.35400000000001</v>
       </c>
       <c r="G19">
         <v>30.4</v>
@@ -2851,28 +2851,28 @@
         <v>17.5</v>
       </c>
       <c r="M19">
-        <v>3.1521553</v>
+        <v>3.3375762</v>
       </c>
       <c r="N19">
-        <v>14.3478447</v>
+        <v>14.1624238</v>
       </c>
       <c r="O19">
-        <v>4.30435341</v>
+        <v>4.24872714</v>
       </c>
       <c r="P19">
-        <v>10.04349129</v>
+        <v>9.913696659999999</v>
       </c>
       <c r="Q19">
-        <v>47.04349129</v>
+        <v>46.91369666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08678309830504952</v>
+        <v>0.08715175554133847</v>
       </c>
       <c r="T19">
-        <v>0.9464918777147693</v>
+        <v>0.9550059016475396</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.551756920098447</v>
+        <v>5.243325980092978</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07843223954389755</v>
+        <v>0.07825380749460399</v>
       </c>
       <c r="C20">
-        <v>244.2889190396664</v>
+        <v>241.9872198929414</v>
       </c>
       <c r="D20">
-        <v>274.2429190396664</v>
+        <v>275.2942198929414</v>
       </c>
       <c r="E20">
-        <v>-104.446</v>
+        <v>-101.093</v>
       </c>
       <c r="F20">
-        <v>60.354</v>
+        <v>63.707</v>
       </c>
       <c r="G20">
         <v>30.4</v>
@@ -2933,28 +2933,28 @@
         <v>17.5</v>
       </c>
       <c r="M20">
-        <v>3.3375762</v>
+        <v>3.5229971</v>
       </c>
       <c r="N20">
-        <v>14.1624238</v>
+        <v>13.9770029</v>
       </c>
       <c r="O20">
-        <v>4.24872714</v>
+        <v>4.19310087</v>
       </c>
       <c r="P20">
-        <v>9.913696659999999</v>
+        <v>9.78390203</v>
       </c>
       <c r="Q20">
-        <v>46.91369666</v>
+        <v>46.78390203</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08715175554133847</v>
+        <v>0.08752951542543702</v>
       </c>
       <c r="T20">
-        <v>0.9550059016475396</v>
+        <v>0.9637301483934649</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.243325980092979</v>
+        <v>4.967361454824927</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07825380749460399</v>
+        <v>0.07807537544531047</v>
       </c>
       <c r="C21">
-        <v>241.9872198929414</v>
+        <v>239.693612015571</v>
       </c>
       <c r="D21">
-        <v>275.2942198929414</v>
+        <v>276.353612015571</v>
       </c>
       <c r="E21">
-        <v>-101.093</v>
+        <v>-97.74000000000001</v>
       </c>
       <c r="F21">
-        <v>63.707</v>
+        <v>67.06</v>
       </c>
       <c r="G21">
         <v>30.4</v>
@@ -3015,28 +3015,28 @@
         <v>17.5</v>
       </c>
       <c r="M21">
-        <v>3.5229971</v>
+        <v>3.708418</v>
       </c>
       <c r="N21">
-        <v>13.9770029</v>
+        <v>13.791582</v>
       </c>
       <c r="O21">
-        <v>4.19310087</v>
+        <v>4.1374746</v>
       </c>
       <c r="P21">
-        <v>9.78390203</v>
+        <v>9.654107400000001</v>
       </c>
       <c r="Q21">
-        <v>46.78390203</v>
+        <v>46.6541074</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08752951542543702</v>
+        <v>0.08791671930663808</v>
       </c>
       <c r="T21">
-        <v>0.9637301483934649</v>
+        <v>0.9726725013080386</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.967361454824927</v>
+        <v>4.71899338208368</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07807537544531047</v>
+        <v>0.07826444339601693</v>
       </c>
       <c r="C22">
-        <v>239.693612015571</v>
+        <v>235.2183285454075</v>
       </c>
       <c r="D22">
-        <v>276.353612015571</v>
+        <v>275.2313285454075</v>
       </c>
       <c r="E22">
-        <v>-97.74000000000001</v>
+        <v>-94.387</v>
       </c>
       <c r="F22">
-        <v>67.06</v>
+        <v>70.41300000000001</v>
       </c>
       <c r="G22">
         <v>30.4</v>
@@ -3097,45 +3097,45 @@
         <v>17.5</v>
       </c>
       <c r="M22">
-        <v>3.708418</v>
+        <v>4.069871400000001</v>
       </c>
       <c r="N22">
-        <v>13.791582</v>
+        <v>13.4301286</v>
       </c>
       <c r="O22">
-        <v>4.1374746</v>
+        <v>4.02903858</v>
       </c>
       <c r="P22">
-        <v>9.654107400000001</v>
+        <v>9.40109002</v>
       </c>
       <c r="Q22">
-        <v>46.6541074</v>
+        <v>46.40109002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08791671930663808</v>
+        <v>0.08831372581774294</v>
       </c>
       <c r="T22">
-        <v>0.9726725013080386</v>
+        <v>0.9818412429039938</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.71899338208368</v>
+        <v>4.29989016360566</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0782644433960169</v>
+        <v>0.07810351134672337</v>
       </c>
       <c r="C23">
-        <v>235.2183285454076</v>
+        <v>232.820021548792</v>
       </c>
       <c r="D23">
-        <v>275.2313285454077</v>
+        <v>276.186021548792</v>
       </c>
       <c r="E23">
-        <v>-94.38700000000001</v>
+        <v>-91.03400000000001</v>
       </c>
       <c r="F23">
-        <v>70.413</v>
+        <v>73.76600000000001</v>
       </c>
       <c r="G23">
         <v>30.4</v>
@@ -3179,28 +3179,28 @@
         <v>17.5</v>
       </c>
       <c r="M23">
-        <v>4.0698714</v>
+        <v>4.2636748</v>
       </c>
       <c r="N23">
-        <v>13.4301286</v>
+        <v>13.2363252</v>
       </c>
       <c r="O23">
-        <v>4.02903858</v>
+        <v>3.97089756</v>
       </c>
       <c r="P23">
-        <v>9.40109002</v>
+        <v>9.26542764</v>
       </c>
       <c r="Q23">
-        <v>46.40109002</v>
+        <v>46.26542764</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08831372581774292</v>
+        <v>0.08872091198297868</v>
       </c>
       <c r="T23">
-        <v>0.9818412429039937</v>
+        <v>0.9912450804383066</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.29989016360566</v>
+        <v>4.104440610714494</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07810351134672337</v>
+        <v>0.07850607929742981</v>
       </c>
       <c r="C24">
-        <v>232.820021548792</v>
+        <v>227.091209035887</v>
       </c>
       <c r="D24">
-        <v>276.186021548792</v>
+        <v>273.8102090358871</v>
       </c>
       <c r="E24">
-        <v>-91.03400000000001</v>
+        <v>-87.68100000000001</v>
       </c>
       <c r="F24">
-        <v>73.76600000000001</v>
+        <v>77.119</v>
       </c>
       <c r="G24">
         <v>30.4</v>
@@ -3261,45 +3261,45 @@
         <v>17.5</v>
       </c>
       <c r="M24">
-        <v>4.2636748</v>
+        <v>4.7273947</v>
       </c>
       <c r="N24">
-        <v>13.2363252</v>
+        <v>12.7726053</v>
       </c>
       <c r="O24">
-        <v>3.97089756</v>
+        <v>3.83178159</v>
       </c>
       <c r="P24">
-        <v>9.26542764</v>
+        <v>8.94082371</v>
       </c>
       <c r="Q24">
-        <v>46.26542764</v>
+        <v>45.94082371</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08872091198297868</v>
+        <v>0.08913867441224652</v>
       </c>
       <c r="T24">
-        <v>0.9912450804383066</v>
+        <v>1.000893173492991</v>
       </c>
       <c r="U24">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.104440610714494</v>
+        <v>3.701827562653062</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07850607929742981</v>
+        <v>0.07836964724813628</v>
       </c>
       <c r="C25">
-        <v>227.091209035887</v>
+        <v>224.5387900278989</v>
       </c>
       <c r="D25">
-        <v>273.8102090358871</v>
+        <v>274.6107900278989</v>
       </c>
       <c r="E25">
-        <v>-87.68100000000001</v>
+        <v>-84.328</v>
       </c>
       <c r="F25">
-        <v>77.119</v>
+        <v>80.47200000000001</v>
       </c>
       <c r="G25">
         <v>30.4</v>
@@ -3343,28 +3343,28 @@
         <v>17.5</v>
       </c>
       <c r="M25">
-        <v>4.7273947</v>
+        <v>4.9329336</v>
       </c>
       <c r="N25">
-        <v>12.7726053</v>
+        <v>12.5670664</v>
       </c>
       <c r="O25">
-        <v>3.83178159</v>
+        <v>3.77011992</v>
       </c>
       <c r="P25">
-        <v>8.94082371</v>
+        <v>8.796946479999999</v>
       </c>
       <c r="Q25">
-        <v>45.94082371</v>
+        <v>45.79694648</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08913867441224652</v>
+        <v>0.089567430589653</v>
       </c>
       <c r="T25">
-        <v>1.000893173492991</v>
+        <v>1.010795163733326</v>
       </c>
       <c r="U25">
         <v>0.0613</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.701827562653062</v>
+        <v>3.547584747542517</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07836964724813628</v>
+        <v>0.07872321519884275</v>
       </c>
       <c r="C26">
-        <v>224.5387900278989</v>
+        <v>219.1206411426579</v>
       </c>
       <c r="D26">
-        <v>274.6107900278989</v>
+        <v>272.5456411426579</v>
       </c>
       <c r="E26">
-        <v>-84.32800000000002</v>
+        <v>-80.97500000000001</v>
       </c>
       <c r="F26">
-        <v>80.47199999999999</v>
+        <v>83.825</v>
       </c>
       <c r="G26">
         <v>30.4</v>
@@ -3425,45 +3425,45 @@
         <v>17.5</v>
       </c>
       <c r="M26">
-        <v>4.932933599999999</v>
+        <v>5.3731825</v>
       </c>
       <c r="N26">
-        <v>12.5670664</v>
+        <v>12.1268175</v>
       </c>
       <c r="O26">
-        <v>3.77011992</v>
+        <v>3.63804525</v>
       </c>
       <c r="P26">
-        <v>8.796946480000001</v>
+        <v>8.48877225</v>
       </c>
       <c r="Q26">
-        <v>45.79694648</v>
+        <v>45.48877225</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.089567430589653</v>
+        <v>0.09000762026512366</v>
       </c>
       <c r="T26">
-        <v>1.010795163733326</v>
+        <v>1.020961207046736</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.547584747542518</v>
+        <v>3.256915245294572</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07872321519884275</v>
+        <v>0.07860638314954918</v>
       </c>
       <c r="C27">
-        <v>219.1206411426579</v>
+        <v>216.4465987671687</v>
       </c>
       <c r="D27">
-        <v>272.5456411426579</v>
+        <v>273.2245987671687</v>
       </c>
       <c r="E27">
-        <v>-80.97500000000001</v>
+        <v>-77.622</v>
       </c>
       <c r="F27">
-        <v>83.825</v>
+        <v>87.17800000000001</v>
       </c>
       <c r="G27">
         <v>30.4</v>
@@ -3507,28 +3507,28 @@
         <v>17.5</v>
       </c>
       <c r="M27">
-        <v>5.3731825</v>
+        <v>5.588109800000001</v>
       </c>
       <c r="N27">
-        <v>12.1268175</v>
+        <v>11.9118902</v>
       </c>
       <c r="O27">
-        <v>3.63804525</v>
+        <v>3.573567059999999</v>
       </c>
       <c r="P27">
-        <v>8.48877225</v>
+        <v>8.33832314</v>
       </c>
       <c r="Q27">
-        <v>45.48877225</v>
+        <v>45.33832314</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09000762026512366</v>
+        <v>0.09045970695885025</v>
       </c>
       <c r="T27">
-        <v>1.020961207046736</v>
+        <v>1.031402008287535</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.256915245294572</v>
+        <v>3.131649274321703</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07860638314954918</v>
+        <v>0.07848955110025566</v>
       </c>
       <c r="C28">
-        <v>216.4465987671687</v>
+        <v>213.7759476380792</v>
       </c>
       <c r="D28">
-        <v>273.2245987671687</v>
+        <v>273.9069476380793</v>
       </c>
       <c r="E28">
-        <v>-77.622</v>
+        <v>-74.26900000000001</v>
       </c>
       <c r="F28">
-        <v>87.17800000000001</v>
+        <v>90.53100000000001</v>
       </c>
       <c r="G28">
         <v>30.4</v>
@@ -3589,28 +3589,28 @@
         <v>17.5</v>
       </c>
       <c r="M28">
-        <v>5.588109800000001</v>
+        <v>5.803037100000001</v>
       </c>
       <c r="N28">
-        <v>11.9118902</v>
+        <v>11.6969629</v>
       </c>
       <c r="O28">
-        <v>3.573567059999999</v>
+        <v>3.50908887</v>
       </c>
       <c r="P28">
-        <v>8.33832314</v>
+        <v>8.18787403</v>
       </c>
       <c r="Q28">
-        <v>45.33832314</v>
+        <v>45.18787403</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09045970695885025</v>
+        <v>0.09092417958939131</v>
       </c>
       <c r="T28">
-        <v>1.031402008287535</v>
+        <v>1.042128858877397</v>
       </c>
       <c r="U28">
         <v>0.0641</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.131649274321703</v>
+        <v>3.01566226416164</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07848955110025566</v>
+        <v>0.0799015190509621</v>
       </c>
       <c r="C29">
-        <v>213.7759476380792</v>
+        <v>202.398067181311</v>
       </c>
       <c r="D29">
-        <v>273.9069476380793</v>
+        <v>265.882067181311</v>
       </c>
       <c r="E29">
-        <v>-74.26900000000001</v>
+        <v>-70.916</v>
       </c>
       <c r="F29">
-        <v>90.53100000000001</v>
+        <v>93.88400000000001</v>
       </c>
       <c r="G29">
         <v>30.4</v>
@@ -3671,45 +3671,45 @@
         <v>17.5</v>
       </c>
       <c r="M29">
-        <v>5.803037100000001</v>
+        <v>6.750259600000001</v>
       </c>
       <c r="N29">
-        <v>11.6969629</v>
+        <v>10.7497404</v>
       </c>
       <c r="O29">
-        <v>3.50908887</v>
+        <v>3.22492212</v>
       </c>
       <c r="P29">
-        <v>8.18787403</v>
+        <v>7.524818279999999</v>
       </c>
       <c r="Q29">
-        <v>45.18787403</v>
+        <v>44.52481828</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09092417958939131</v>
+        <v>0.09140155423744736</v>
       </c>
       <c r="T29">
-        <v>1.042128858877397</v>
+        <v>1.0531536775392</v>
       </c>
       <c r="U29">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.01566226416164</v>
+        <v>2.592492887236514</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0799015190509621</v>
+        <v>0.07983928700166856</v>
       </c>
       <c r="C30">
-        <v>202.398067181311</v>
+        <v>199.3888427405629</v>
       </c>
       <c r="D30">
-        <v>265.882067181311</v>
+        <v>266.225842740563</v>
       </c>
       <c r="E30">
-        <v>-70.916</v>
+        <v>-67.563</v>
       </c>
       <c r="F30">
-        <v>93.88400000000001</v>
+        <v>97.23700000000001</v>
       </c>
       <c r="G30">
         <v>30.4</v>
@@ -3753,28 +3753,28 @@
         <v>17.5</v>
       </c>
       <c r="M30">
-        <v>6.750259600000001</v>
+        <v>6.991340300000001</v>
       </c>
       <c r="N30">
-        <v>10.7497404</v>
+        <v>10.5086597</v>
       </c>
       <c r="O30">
-        <v>3.22492212</v>
+        <v>3.152597909999999</v>
       </c>
       <c r="P30">
-        <v>7.524818279999999</v>
+        <v>7.35606179</v>
       </c>
       <c r="Q30">
-        <v>44.52481828</v>
+        <v>44.35606179</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09140155423744736</v>
+        <v>0.09189237605868811</v>
       </c>
       <c r="T30">
-        <v>1.0531536775392</v>
+        <v>1.064489054473167</v>
       </c>
       <c r="U30">
         <v>0.07190000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.592492887236514</v>
+        <v>2.503096580780083</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07983928700166856</v>
+        <v>0.08059605495237501</v>
       </c>
       <c r="C31">
-        <v>199.388842740563</v>
+        <v>191.9147772513436</v>
       </c>
       <c r="D31">
-        <v>266.225842740563</v>
+        <v>262.1047772513436</v>
       </c>
       <c r="E31">
-        <v>-67.56300000000002</v>
+        <v>-64.21000000000001</v>
       </c>
       <c r="F31">
-        <v>97.23699999999999</v>
+        <v>100.59</v>
       </c>
       <c r="G31">
         <v>30.4</v>
@@ -3835,45 +3835,45 @@
         <v>17.5</v>
       </c>
       <c r="M31">
-        <v>6.9913403</v>
+        <v>7.624722000000001</v>
       </c>
       <c r="N31">
-        <v>10.5086597</v>
+        <v>9.875277999999998</v>
       </c>
       <c r="O31">
-        <v>3.152597909999999</v>
+        <v>2.962583399999999</v>
       </c>
       <c r="P31">
-        <v>7.35606179</v>
+        <v>6.912694599999998</v>
       </c>
       <c r="Q31">
-        <v>44.35606179</v>
+        <v>43.91269459999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09189237605868811</v>
+        <v>0.09239722136053574</v>
       </c>
       <c r="T31">
-        <v>1.064489054473167</v>
+        <v>1.076148299319532</v>
       </c>
       <c r="U31">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.503096580780083</v>
+        <v>2.295165646695053</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08059605495237501</v>
+        <v>0.08056112290308146</v>
       </c>
       <c r="C32">
-        <v>191.9147772513436</v>
+        <v>188.7491929657767</v>
       </c>
       <c r="D32">
-        <v>262.1047772513436</v>
+        <v>262.2921929657767</v>
       </c>
       <c r="E32">
-        <v>-64.21000000000001</v>
+        <v>-60.85700000000001</v>
       </c>
       <c r="F32">
-        <v>100.59</v>
+        <v>103.943</v>
       </c>
       <c r="G32">
         <v>30.4</v>
@@ -3917,28 +3917,28 @@
         <v>17.5</v>
       </c>
       <c r="M32">
-        <v>7.624722000000001</v>
+        <v>7.878879400000001</v>
       </c>
       <c r="N32">
-        <v>9.875277999999998</v>
+        <v>9.621120599999999</v>
       </c>
       <c r="O32">
-        <v>2.962583399999999</v>
+        <v>2.88633618</v>
       </c>
       <c r="P32">
-        <v>6.912694599999998</v>
+        <v>6.73478442</v>
       </c>
       <c r="Q32">
-        <v>43.91269459999999</v>
+        <v>43.73478442</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09239722136053574</v>
+        <v>0.09291669985953836</v>
       </c>
       <c r="T32">
-        <v>1.076148299319532</v>
+        <v>1.088145493291879</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.295165646695053</v>
+        <v>2.221128045188761</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08056112290308146</v>
+        <v>0.08052619085378793</v>
       </c>
       <c r="C33">
-        <v>188.7491929657767</v>
+        <v>185.5838768919068</v>
       </c>
       <c r="D33">
-        <v>262.2921929657767</v>
+        <v>262.4798768919068</v>
       </c>
       <c r="E33">
-        <v>-60.85700000000001</v>
+        <v>-57.504</v>
       </c>
       <c r="F33">
-        <v>103.943</v>
+        <v>107.296</v>
       </c>
       <c r="G33">
         <v>30.4</v>
@@ -3999,28 +3999,28 @@
         <v>17.5</v>
       </c>
       <c r="M33">
-        <v>7.878879400000001</v>
+        <v>8.133036800000001</v>
       </c>
       <c r="N33">
-        <v>9.621120599999999</v>
+        <v>9.366963199999999</v>
       </c>
       <c r="O33">
-        <v>2.88633618</v>
+        <v>2.810088959999999</v>
       </c>
       <c r="P33">
-        <v>6.73478442</v>
+        <v>6.556874239999999</v>
       </c>
       <c r="Q33">
-        <v>43.73478442</v>
+        <v>43.55687424</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09291669985953836</v>
+        <v>0.09345145713792342</v>
       </c>
       <c r="T33">
-        <v>1.088145493291879</v>
+        <v>1.100495545910472</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.221128045188761</v>
+        <v>2.151717793776612</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08052619085378793</v>
+        <v>0.08049125880449438</v>
       </c>
       <c r="C34">
-        <v>185.5838768919068</v>
+        <v>182.4188296059052</v>
       </c>
       <c r="D34">
-        <v>262.4798768919068</v>
+        <v>262.6678296059052</v>
       </c>
       <c r="E34">
-        <v>-57.504</v>
+        <v>-54.151</v>
       </c>
       <c r="F34">
-        <v>107.296</v>
+        <v>110.649</v>
       </c>
       <c r="G34">
         <v>30.4</v>
@@ -4081,28 +4081,28 @@
         <v>17.5</v>
       </c>
       <c r="M34">
-        <v>8.133036800000001</v>
+        <v>8.387194200000001</v>
       </c>
       <c r="N34">
-        <v>9.366963199999999</v>
+        <v>9.112805799999999</v>
       </c>
       <c r="O34">
-        <v>2.810088959999999</v>
+        <v>2.733841739999999</v>
       </c>
       <c r="P34">
-        <v>6.556874239999999</v>
+        <v>6.378964059999999</v>
       </c>
       <c r="Q34">
-        <v>43.55687424</v>
+        <v>43.37896406</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09345145713792342</v>
+        <v>0.09400217732014088</v>
       </c>
       <c r="T34">
-        <v>1.100495545910472</v>
+        <v>1.113214256816186</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.151717793776612</v>
+        <v>2.08651422426823</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08049125880449438</v>
+        <v>0.08045632675520084</v>
       </c>
       <c r="C35">
-        <v>182.4188296059052</v>
+        <v>179.2540516855946</v>
       </c>
       <c r="D35">
-        <v>262.6678296059052</v>
+        <v>262.8560516855946</v>
       </c>
       <c r="E35">
-        <v>-54.151</v>
+        <v>-50.798</v>
       </c>
       <c r="F35">
-        <v>110.649</v>
+        <v>114.002</v>
       </c>
       <c r="G35">
         <v>30.4</v>
@@ -4163,28 +4163,28 @@
         <v>17.5</v>
       </c>
       <c r="M35">
-        <v>8.387194200000001</v>
+        <v>8.641351600000002</v>
       </c>
       <c r="N35">
-        <v>9.112805799999999</v>
+        <v>8.858648399999998</v>
       </c>
       <c r="O35">
-        <v>2.733841739999999</v>
+        <v>2.65759452</v>
       </c>
       <c r="P35">
-        <v>6.378964059999999</v>
+        <v>6.201053879999998</v>
       </c>
       <c r="Q35">
-        <v>43.37896406</v>
+        <v>43.20105388</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09400217732014088</v>
+        <v>0.09456958599272855</v>
       </c>
       <c r="T35">
-        <v>1.113214256816186</v>
+        <v>1.126318383203893</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.08651422426823</v>
+        <v>2.025146158848576</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08045632675520084</v>
+        <v>0.08390039470590729</v>
       </c>
       <c r="C36">
-        <v>179.2540516855946</v>
+        <v>158.5557505860218</v>
       </c>
       <c r="D36">
-        <v>262.8560516855946</v>
+        <v>245.5107505860218</v>
       </c>
       <c r="E36">
-        <v>-50.798</v>
+        <v>-47.44499999999999</v>
       </c>
       <c r="F36">
-        <v>114.002</v>
+        <v>117.355</v>
       </c>
       <c r="G36">
         <v>30.4</v>
@@ -4245,45 +4245,45 @@
         <v>17.5</v>
       </c>
       <c r="M36">
-        <v>8.641351600000002</v>
+        <v>10.56195</v>
       </c>
       <c r="N36">
-        <v>8.858648399999998</v>
+        <v>6.938049999999999</v>
       </c>
       <c r="O36">
-        <v>2.65759452</v>
+        <v>2.081414999999999</v>
       </c>
       <c r="P36">
-        <v>6.201053879999998</v>
+        <v>4.856634999999999</v>
       </c>
       <c r="Q36">
-        <v>43.20105388</v>
+        <v>41.856635</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09456958599272855</v>
+        <v>0.09515445339370353</v>
       </c>
       <c r="T36">
-        <v>1.126318383203893</v>
+        <v>1.139825713480451</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.025146158848576</v>
+        <v>1.656891009709381</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08390039470590729</v>
+        <v>0.08396486265661375</v>
       </c>
       <c r="C37">
-        <v>158.5557505860218</v>
+        <v>154.8998707071466</v>
       </c>
       <c r="D37">
-        <v>245.5107505860218</v>
+        <v>245.2078707071467</v>
       </c>
       <c r="E37">
-        <v>-47.44499999999999</v>
+        <v>-44.092</v>
       </c>
       <c r="F37">
-        <v>117.355</v>
+        <v>120.708</v>
       </c>
       <c r="G37">
         <v>30.4</v>
@@ -4327,28 +4327,28 @@
         <v>17.5</v>
       </c>
       <c r="M37">
-        <v>10.56195</v>
+        <v>10.86372</v>
       </c>
       <c r="N37">
-        <v>6.938049999999999</v>
+        <v>6.636279999999999</v>
       </c>
       <c r="O37">
-        <v>2.081414999999999</v>
+        <v>1.990884</v>
       </c>
       <c r="P37">
-        <v>4.856634999999999</v>
+        <v>4.645396</v>
       </c>
       <c r="Q37">
-        <v>41.856635</v>
+        <v>41.645396</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09515445339370353</v>
+        <v>0.09575759790095899</v>
       </c>
       <c r="T37">
-        <v>1.139825713480451</v>
+        <v>1.153755147828152</v>
       </c>
       <c r="U37">
         <v>0.09</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>1.656891009709381</v>
+        <v>1.610866259439676</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08396486265661375</v>
+        <v>0.08402933060732021</v>
       </c>
       <c r="C38">
-        <v>154.8998707071467</v>
+        <v>151.2447372166704</v>
       </c>
       <c r="D38">
-        <v>245.2078707071467</v>
+        <v>244.9057372166704</v>
       </c>
       <c r="E38">
-        <v>-44.09200000000001</v>
+        <v>-40.739</v>
       </c>
       <c r="F38">
-        <v>120.708</v>
+        <v>124.061</v>
       </c>
       <c r="G38">
         <v>30.4</v>
@@ -4409,28 +4409,28 @@
         <v>17.5</v>
       </c>
       <c r="M38">
-        <v>10.86372</v>
+        <v>11.16549</v>
       </c>
       <c r="N38">
-        <v>6.636280000000001</v>
+        <v>6.33451</v>
       </c>
       <c r="O38">
-        <v>1.990884</v>
+        <v>1.900353</v>
       </c>
       <c r="P38">
-        <v>4.645396000000001</v>
+        <v>4.434157</v>
       </c>
       <c r="Q38">
-        <v>41.645396</v>
+        <v>41.434157</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09575759790095899</v>
+        <v>0.09637988985288921</v>
       </c>
       <c r="T38">
-        <v>1.153755147828152</v>
+        <v>1.16812678644086</v>
       </c>
       <c r="U38">
         <v>0.09</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.610866259439677</v>
+        <v>1.567329333508874</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08402933060732021</v>
+        <v>0.08409379855802665</v>
       </c>
       <c r="C39">
-        <v>151.2447372166704</v>
+        <v>147.5903473589954</v>
       </c>
       <c r="D39">
-        <v>244.9057372166704</v>
+        <v>244.6043473589953</v>
       </c>
       <c r="E39">
-        <v>-40.739</v>
+        <v>-37.38600000000001</v>
       </c>
       <c r="F39">
-        <v>124.061</v>
+        <v>127.414</v>
       </c>
       <c r="G39">
         <v>30.4</v>
@@ -4491,28 +4491,28 @@
         <v>17.5</v>
       </c>
       <c r="M39">
-        <v>11.16549</v>
+        <v>11.46726</v>
       </c>
       <c r="N39">
-        <v>6.33451</v>
+        <v>6.03274</v>
       </c>
       <c r="O39">
-        <v>1.900353</v>
+        <v>1.809822</v>
       </c>
       <c r="P39">
-        <v>4.434157</v>
+        <v>4.222918</v>
       </c>
       <c r="Q39">
-        <v>41.434157</v>
+        <v>41.222918</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09637988985288921</v>
+        <v>0.09702225573875267</v>
       </c>
       <c r="T39">
-        <v>1.16812678644086</v>
+        <v>1.182962026299138</v>
       </c>
       <c r="U39">
         <v>0.09</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.567329333508874</v>
+        <v>1.526083824732325</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08409379855802665</v>
+        <v>0.1015532901901783</v>
       </c>
       <c r="C40">
-        <v>147.5903473589954</v>
+        <v>83.09273825765135</v>
       </c>
       <c r="D40">
-        <v>244.6043473589953</v>
+        <v>183.4597382576513</v>
       </c>
       <c r="E40">
-        <v>-37.38600000000001</v>
+        <v>-34.03300000000002</v>
       </c>
       <c r="F40">
-        <v>127.414</v>
+        <v>130.767</v>
       </c>
       <c r="G40">
         <v>30.4</v>
@@ -4573,45 +4573,45 @@
         <v>17.5</v>
       </c>
       <c r="M40">
-        <v>11.46726</v>
+        <v>19.1965956</v>
       </c>
       <c r="N40">
-        <v>6.03274</v>
+        <v>-1.696595600000002</v>
       </c>
       <c r="O40">
-        <v>1.809822</v>
+        <v>-0.5089786800000006</v>
       </c>
       <c r="P40">
-        <v>4.222918</v>
+        <v>-1.187616920000001</v>
       </c>
       <c r="Q40">
-        <v>41.222918</v>
+        <v>35.81238308</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09702225573875267</v>
+        <v>0.09829329546218349</v>
       </c>
       <c r="T40">
-        <v>1.182962026299138</v>
+        <v>1.21231629242918</v>
       </c>
       <c r="U40">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.3</v>
+        <v>0.2734859924850425</v>
       </c>
       <c r="W40">
-        <v>0.063</v>
+        <v>0.1066522563031958</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y40">
-        <v>1.526083824732325</v>
+        <v>0.9116199749501416</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1015532901901783</v>
+        <v>0.1025632901901783</v>
       </c>
       <c r="C41">
-        <v>83.09273825765135</v>
+        <v>77.12463162486472</v>
       </c>
       <c r="D41">
-        <v>183.4597382576513</v>
+        <v>180.8446316248647</v>
       </c>
       <c r="E41">
-        <v>-34.03300000000002</v>
+        <v>-30.68000000000001</v>
       </c>
       <c r="F41">
-        <v>130.767</v>
+        <v>134.12</v>
       </c>
       <c r="G41">
         <v>30.4</v>
@@ -4655,37 +4655,37 @@
         <v>17.5</v>
       </c>
       <c r="M41">
-        <v>19.1965956</v>
+        <v>19.688816</v>
       </c>
       <c r="N41">
-        <v>-1.696595600000002</v>
+        <v>-2.188816000000003</v>
       </c>
       <c r="O41">
-        <v>-0.5089786800000006</v>
+        <v>-0.6566448000000008</v>
       </c>
       <c r="P41">
-        <v>-1.187616920000001</v>
+        <v>-1.532171200000002</v>
       </c>
       <c r="Q41">
-        <v>35.81238308</v>
+        <v>35.4678288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09829329546218349</v>
+        <v>0.09916818371988656</v>
       </c>
       <c r="T41">
-        <v>1.21231629242918</v>
+        <v>1.232521563969667</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.2734859924850425</v>
+        <v>0.2666488426729164</v>
       </c>
       <c r="W41">
-        <v>0.1066522563031958</v>
+        <v>0.1076559498956159</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.9116199749501416</v>
+        <v>0.888829475576388</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1025632901901783</v>
+        <v>0.1035732901901783</v>
       </c>
       <c r="C42">
-        <v>77.12463162486472</v>
+        <v>71.2300307118316</v>
       </c>
       <c r="D42">
-        <v>180.8446316248647</v>
+        <v>178.3030307118316</v>
       </c>
       <c r="E42">
-        <v>-30.68000000000001</v>
+        <v>-27.327</v>
       </c>
       <c r="F42">
-        <v>134.12</v>
+        <v>137.473</v>
       </c>
       <c r="G42">
         <v>30.4</v>
@@ -4737,37 +4737,37 @@
         <v>17.5</v>
       </c>
       <c r="M42">
-        <v>19.688816</v>
+        <v>20.1810364</v>
       </c>
       <c r="N42">
-        <v>-2.188816000000003</v>
+        <v>-2.681036400000004</v>
       </c>
       <c r="O42">
-        <v>-0.6566448000000008</v>
+        <v>-0.804310920000001</v>
       </c>
       <c r="P42">
-        <v>-1.532171200000002</v>
+        <v>-1.876725480000002</v>
       </c>
       <c r="Q42">
-        <v>35.4678288</v>
+        <v>35.12327452</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09916818371988656</v>
+        <v>0.1000727292066643</v>
       </c>
       <c r="T42">
-        <v>1.232521563969667</v>
+        <v>1.253411759969153</v>
       </c>
       <c r="U42">
         <v>0.1468</v>
       </c>
       <c r="V42">
-        <v>0.2666488426729164</v>
+        <v>0.2601452123638209</v>
       </c>
       <c r="W42">
-        <v>0.1076559498956159</v>
+        <v>0.1086106828249911</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.888829475576388</v>
+        <v>0.867150707879403</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1035732901901783</v>
+        <v>0.1045832901901783</v>
       </c>
       <c r="C43">
-        <v>71.2300307118316</v>
+        <v>65.40587930977571</v>
       </c>
       <c r="D43">
-        <v>178.3030307118316</v>
+        <v>175.8318793097757</v>
       </c>
       <c r="E43">
-        <v>-27.327</v>
+        <v>-23.97399999999999</v>
       </c>
       <c r="F43">
-        <v>137.473</v>
+        <v>140.826</v>
       </c>
       <c r="G43">
         <v>30.4</v>
@@ -4819,37 +4819,37 @@
         <v>17.5</v>
       </c>
       <c r="M43">
-        <v>20.1810364</v>
+        <v>20.6732568</v>
       </c>
       <c r="N43">
-        <v>-2.681036400000004</v>
+        <v>-3.173256800000004</v>
       </c>
       <c r="O43">
-        <v>-0.804310920000001</v>
+        <v>-0.9519770400000013</v>
       </c>
       <c r="P43">
-        <v>-1.876725480000002</v>
+        <v>-2.221279760000003</v>
       </c>
       <c r="Q43">
-        <v>35.12327452</v>
+        <v>34.77872024</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1000727292066643</v>
+        <v>0.101008465917124</v>
       </c>
       <c r="T43">
-        <v>1.253411759969153</v>
+        <v>1.275022307554827</v>
       </c>
       <c r="U43">
         <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2601452123638209</v>
+        <v>0.2539512787361108</v>
       </c>
       <c r="W43">
-        <v>0.1086106828249911</v>
+        <v>0.1095199522815389</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.867150707879403</v>
+        <v>0.8465042624537028</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1045832901901783</v>
+        <v>0.1055932901901783</v>
       </c>
       <c r="C44">
-        <v>65.40587930977574</v>
+        <v>59.64928832127538</v>
       </c>
       <c r="D44">
-        <v>175.8318793097757</v>
+        <v>173.4282883212754</v>
       </c>
       <c r="E44">
-        <v>-23.97400000000002</v>
+        <v>-20.62100000000001</v>
       </c>
       <c r="F44">
-        <v>140.826</v>
+        <v>144.179</v>
       </c>
       <c r="G44">
         <v>30.4</v>
@@ -4901,37 +4901,37 @@
         <v>17.5</v>
       </c>
       <c r="M44">
-        <v>20.6732568</v>
+        <v>21.1654772</v>
       </c>
       <c r="N44">
-        <v>-3.173256800000001</v>
+        <v>-3.665477200000002</v>
       </c>
       <c r="O44">
-        <v>-0.9519770400000002</v>
+        <v>-1.099643160000001</v>
       </c>
       <c r="P44">
-        <v>-2.221279760000001</v>
+        <v>-2.565834040000001</v>
       </c>
       <c r="Q44">
-        <v>34.77872024</v>
+        <v>34.43416596</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.101008465917124</v>
+        <v>0.1019770354946174</v>
       </c>
       <c r="T44">
-        <v>1.275022307554827</v>
+        <v>1.29739111996807</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.2539512787361108</v>
+        <v>0.2480454350445734</v>
       </c>
       <c r="W44">
-        <v>0.1095199522815389</v>
+        <v>0.1103869301354566</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8465042624537029</v>
+        <v>0.8268181168152448</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1055932901901783</v>
+        <v>0.1066032901901783</v>
       </c>
       <c r="C45">
-        <v>59.64928832127538</v>
+        <v>53.95752449237821</v>
       </c>
       <c r="D45">
-        <v>173.4282883212754</v>
+        <v>171.0895244923782</v>
       </c>
       <c r="E45">
-        <v>-20.62100000000001</v>
+        <v>-17.268</v>
       </c>
       <c r="F45">
-        <v>144.179</v>
+        <v>147.532</v>
       </c>
       <c r="G45">
         <v>30.4</v>
@@ -4983,37 +4983,37 @@
         <v>17.5</v>
       </c>
       <c r="M45">
-        <v>21.1654772</v>
+        <v>21.6576976</v>
       </c>
       <c r="N45">
-        <v>-3.665477200000002</v>
+        <v>-4.157697600000002</v>
       </c>
       <c r="O45">
-        <v>-1.099643160000001</v>
+        <v>-1.247309280000001</v>
       </c>
       <c r="P45">
-        <v>-2.565834040000001</v>
+        <v>-2.910388320000002</v>
       </c>
       <c r="Q45">
-        <v>34.43416596</v>
+        <v>34.08961168</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1019770354946174</v>
+        <v>0.1029801968427356</v>
       </c>
       <c r="T45">
-        <v>1.29739111996807</v>
+        <v>1.320558818538929</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.2480454350445734</v>
+        <v>0.2424080387935603</v>
       </c>
       <c r="W45">
-        <v>0.1103869301354566</v>
+        <v>0.1112144999051054</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8268181168152448</v>
+        <v>0.8080267959785346</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1066032901901783</v>
+        <v>0.1329414163592991</v>
       </c>
       <c r="C46">
-        <v>53.95752449237821</v>
+        <v>6.091810181958806</v>
       </c>
       <c r="D46">
-        <v>171.0895244923782</v>
+        <v>126.5768101819588</v>
       </c>
       <c r="E46">
-        <v>-17.268</v>
+        <v>-13.91499999999999</v>
       </c>
       <c r="F46">
-        <v>147.532</v>
+        <v>150.885</v>
       </c>
       <c r="G46">
         <v>30.4</v>
@@ -5065,45 +5065,45 @@
         <v>17.5</v>
       </c>
       <c r="M46">
-        <v>21.6576976</v>
+        <v>30.297708</v>
       </c>
       <c r="N46">
-        <v>-4.157697600000002</v>
+        <v>-12.797708</v>
       </c>
       <c r="O46">
-        <v>-1.247309280000001</v>
+        <v>-3.839312400000001</v>
       </c>
       <c r="P46">
-        <v>-2.910388320000002</v>
+        <v>-8.958395600000003</v>
       </c>
       <c r="Q46">
-        <v>34.08961168</v>
+        <v>28.0416044</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1029801968427356</v>
+        <v>0.1058891570928232</v>
       </c>
       <c r="T46">
-        <v>1.320558818538929</v>
+        <v>1.387740348564047</v>
       </c>
       <c r="U46">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.2424080387935603</v>
+        <v>0.1732804342823556</v>
       </c>
       <c r="W46">
-        <v>0.1112144999051054</v>
+        <v>0.166005288796103</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.8080267959785346</v>
+        <v>0.5776014476078519</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1329414163592991</v>
+        <v>0.1344914163592991</v>
       </c>
       <c r="C47">
-        <v>6.091810181958806</v>
+        <v>0.8300011595320598</v>
       </c>
       <c r="D47">
-        <v>126.5768101819588</v>
+        <v>124.6680011595321</v>
       </c>
       <c r="E47">
-        <v>-13.91499999999999</v>
+        <v>-10.56200000000001</v>
       </c>
       <c r="F47">
-        <v>150.885</v>
+        <v>154.238</v>
       </c>
       <c r="G47">
         <v>30.4</v>
@@ -5147,37 +5147,37 @@
         <v>17.5</v>
       </c>
       <c r="M47">
-        <v>30.297708</v>
+        <v>30.9709904</v>
       </c>
       <c r="N47">
-        <v>-12.797708</v>
+        <v>-13.4709904</v>
       </c>
       <c r="O47">
-        <v>-3.839312400000001</v>
+        <v>-4.04129712</v>
       </c>
       <c r="P47">
-        <v>-8.958395600000003</v>
+        <v>-9.429693280000002</v>
       </c>
       <c r="Q47">
-        <v>28.0416044</v>
+        <v>27.57030672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1058891570928232</v>
+        <v>0.1070019192612089</v>
       </c>
       <c r="T47">
-        <v>1.387740348564047</v>
+        <v>1.413439243907826</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1732804342823556</v>
+        <v>0.1695134683196957</v>
       </c>
       <c r="W47">
-        <v>0.166005288796103</v>
+        <v>0.1667616955614051</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5776014476078519</v>
+        <v>0.5650448943989856</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1344914163592991</v>
+        <v>0.1360414163592991</v>
       </c>
       <c r="C48">
-        <v>0.8300011595320598</v>
+        <v>-4.375092536982578</v>
       </c>
       <c r="D48">
-        <v>124.6680011595321</v>
+        <v>122.8159074630174</v>
       </c>
       <c r="E48">
-        <v>-10.56200000000001</v>
+        <v>-7.209000000000003</v>
       </c>
       <c r="F48">
-        <v>154.238</v>
+        <v>157.591</v>
       </c>
       <c r="G48">
         <v>30.4</v>
@@ -5229,37 +5229,37 @@
         <v>17.5</v>
       </c>
       <c r="M48">
-        <v>30.9709904</v>
+        <v>31.6442728</v>
       </c>
       <c r="N48">
-        <v>-13.4709904</v>
+        <v>-14.1442728</v>
       </c>
       <c r="O48">
-        <v>-4.04129712</v>
+        <v>-4.243281840000001</v>
       </c>
       <c r="P48">
-        <v>-9.429693280000002</v>
+        <v>-9.900990960000001</v>
       </c>
       <c r="Q48">
-        <v>27.57030672</v>
+        <v>27.09900904</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1070019192612089</v>
+        <v>0.1081566724548166</v>
       </c>
       <c r="T48">
-        <v>1.413439243907826</v>
+        <v>1.440107908887219</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1695134683196957</v>
+        <v>0.1659067987809788</v>
       </c>
       <c r="W48">
-        <v>0.1667616955614051</v>
+        <v>0.1674859148047795</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5650448943989856</v>
+        <v>0.5530226626032626</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1360414163592991</v>
+        <v>0.1375914163592991</v>
       </c>
       <c r="C49">
-        <v>-4.375092536982578</v>
+        <v>-9.525961628867094</v>
       </c>
       <c r="D49">
-        <v>122.8159074630174</v>
+        <v>121.0180383711329</v>
       </c>
       <c r="E49">
-        <v>-7.209000000000003</v>
+        <v>-3.855999999999995</v>
       </c>
       <c r="F49">
-        <v>157.591</v>
+        <v>160.944</v>
       </c>
       <c r="G49">
         <v>30.4</v>
@@ -5311,37 +5311,37 @@
         <v>17.5</v>
       </c>
       <c r="M49">
-        <v>31.6442728</v>
+        <v>32.3175552</v>
       </c>
       <c r="N49">
-        <v>-14.1442728</v>
+        <v>-14.8175552</v>
       </c>
       <c r="O49">
-        <v>-4.243281840000001</v>
+        <v>-4.44526656</v>
       </c>
       <c r="P49">
-        <v>-9.900990960000001</v>
+        <v>-10.37228864</v>
       </c>
       <c r="Q49">
-        <v>27.09900904</v>
+        <v>26.62771136</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1081566724548166</v>
+        <v>0.1093558392327938</v>
       </c>
       <c r="T49">
-        <v>1.440107908887219</v>
+        <v>1.467802291750435</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1659067987809788</v>
+        <v>0.1624504071397084</v>
       </c>
       <c r="W49">
-        <v>0.1674859148047795</v>
+        <v>0.1681799582463466</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.5530226626032626</v>
+        <v>0.5415013571323612</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1375914163592991</v>
+        <v>0.1391414163592991</v>
       </c>
       <c r="C50">
-        <v>-9.525961628867066</v>
+        <v>-14.6249530975719</v>
       </c>
       <c r="D50">
-        <v>121.0180383711329</v>
+        <v>119.2720469024281</v>
       </c>
       <c r="E50">
-        <v>-3.856000000000023</v>
+        <v>-0.5030000000000143</v>
       </c>
       <c r="F50">
-        <v>160.944</v>
+        <v>164.297</v>
       </c>
       <c r="G50">
         <v>30.4</v>
@@ -5393,37 +5393,37 @@
         <v>17.5</v>
       </c>
       <c r="M50">
-        <v>32.3175552</v>
+        <v>32.9908376</v>
       </c>
       <c r="N50">
-        <v>-14.8175552</v>
+        <v>-15.4908376</v>
       </c>
       <c r="O50">
-        <v>-4.44526656</v>
+        <v>-4.64725128</v>
       </c>
       <c r="P50">
-        <v>-10.37228864</v>
+        <v>-10.84358632</v>
       </c>
       <c r="Q50">
-        <v>26.62771136</v>
+        <v>26.15641368</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1093558392327938</v>
+        <v>0.1106020321589271</v>
       </c>
       <c r="T50">
-        <v>1.467802291750435</v>
+        <v>1.496582728843581</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1624504071397084</v>
+        <v>0.1591350927082858</v>
       </c>
       <c r="W50">
-        <v>0.1681799582463466</v>
+        <v>0.1688456733841762</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.5415013571323612</v>
+        <v>0.5304503090276192</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1391414163592991</v>
+        <v>0.1406914163592992</v>
       </c>
       <c r="C51">
-        <v>-14.6249530975719</v>
+        <v>-19.67428040629818</v>
       </c>
       <c r="D51">
-        <v>119.2720469024281</v>
+        <v>117.5757195937018</v>
       </c>
       <c r="E51">
-        <v>-0.5030000000000143</v>
+        <v>2.849999999999994</v>
       </c>
       <c r="F51">
-        <v>164.297</v>
+        <v>167.65</v>
       </c>
       <c r="G51">
         <v>30.4</v>
@@ -5475,37 +5475,37 @@
         <v>17.5</v>
       </c>
       <c r="M51">
-        <v>32.9908376</v>
+        <v>33.66412</v>
       </c>
       <c r="N51">
-        <v>-15.4908376</v>
+        <v>-16.16412</v>
       </c>
       <c r="O51">
-        <v>-4.64725128</v>
+        <v>-4.849236000000001</v>
       </c>
       <c r="P51">
-        <v>-10.84358632</v>
+        <v>-11.314884</v>
       </c>
       <c r="Q51">
-        <v>26.15641368</v>
+        <v>25.685116</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1106020321589271</v>
+        <v>0.1118980728021056</v>
       </c>
       <c r="T51">
-        <v>1.496582728843581</v>
+        <v>1.526514383420452</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1591350927082858</v>
+        <v>0.15595239085412</v>
       </c>
       <c r="W51">
-        <v>0.1688456733841762</v>
+        <v>0.1694847599164927</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5304503090276192</v>
+        <v>0.5198413028470668</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1406914163592992</v>
+        <v>0.1422414163592992</v>
       </c>
       <c r="C52">
-        <v>-19.67428040629818</v>
+        <v>-24.67603286156222</v>
       </c>
       <c r="D52">
-        <v>117.5757195937018</v>
+        <v>115.9269671384378</v>
       </c>
       <c r="E52">
-        <v>2.849999999999994</v>
+        <v>6.203000000000003</v>
       </c>
       <c r="F52">
-        <v>167.65</v>
+        <v>171.003</v>
       </c>
       <c r="G52">
         <v>30.4</v>
@@ -5557,37 +5557,37 @@
         <v>17.5</v>
       </c>
       <c r="M52">
-        <v>33.66412</v>
+        <v>34.3374024</v>
       </c>
       <c r="N52">
-        <v>-16.16412</v>
+        <v>-16.8374024</v>
       </c>
       <c r="O52">
-        <v>-4.849236000000001</v>
+        <v>-5.051220720000001</v>
       </c>
       <c r="P52">
-        <v>-11.314884</v>
+        <v>-11.78618168</v>
       </c>
       <c r="Q52">
-        <v>25.685116</v>
+        <v>25.21381832</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1118980728021056</v>
+        <v>0.113247013063373</v>
       </c>
       <c r="T52">
-        <v>1.526514383420452</v>
+        <v>1.557667738184135</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.15595239085412</v>
+        <v>0.1528945008373726</v>
       </c>
       <c r="W52">
-        <v>0.1694847599164927</v>
+        <v>0.1700987842318556</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5198413028470668</v>
+        <v>0.5096483361245754</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1422414163592992</v>
+        <v>0.1624062776869264</v>
       </c>
       <c r="C53">
-        <v>-24.67603286156222</v>
+        <v>-45.91488350395412</v>
       </c>
       <c r="D53">
-        <v>115.9269671384378</v>
+        <v>98.0411164960459</v>
       </c>
       <c r="E53">
-        <v>6.203000000000003</v>
+        <v>9.556000000000012</v>
       </c>
       <c r="F53">
-        <v>171.003</v>
+        <v>174.356</v>
       </c>
       <c r="G53">
         <v>30.4</v>
@@ -5639,45 +5639,45 @@
         <v>17.5</v>
       </c>
       <c r="M53">
-        <v>34.3374024</v>
+        <v>41.11314480000001</v>
       </c>
       <c r="N53">
-        <v>-16.8374024</v>
+        <v>-23.61314480000001</v>
       </c>
       <c r="O53">
-        <v>-5.051220720000001</v>
+        <v>-7.083943440000002</v>
       </c>
       <c r="P53">
-        <v>-11.78618168</v>
+        <v>-16.52920136000001</v>
       </c>
       <c r="Q53">
-        <v>25.21381832</v>
+        <v>20.47079863999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.113247013063373</v>
+        <v>0.1155164536014167</v>
       </c>
       <c r="T53">
-        <v>1.557667738184135</v>
+        <v>1.610079759847961</v>
       </c>
       <c r="U53">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1528945008373726</v>
+        <v>0.1276963858040847</v>
       </c>
       <c r="W53">
-        <v>0.1700987842318556</v>
+        <v>0.2056891922273968</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.5096483361245754</v>
+        <v>0.425654619346949</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1624062776869264</v>
+        <v>0.1643062776869264</v>
       </c>
       <c r="C54">
-        <v>-45.91488350395412</v>
+        <v>-50.67271333389027</v>
       </c>
       <c r="D54">
-        <v>98.0411164960459</v>
+        <v>96.63628666610973</v>
       </c>
       <c r="E54">
-        <v>9.556000000000012</v>
+        <v>12.90899999999999</v>
       </c>
       <c r="F54">
-        <v>174.356</v>
+        <v>177.709</v>
       </c>
       <c r="G54">
         <v>30.4</v>
@@ -5721,37 +5721,37 @@
         <v>17.5</v>
       </c>
       <c r="M54">
-        <v>41.11314480000001</v>
+        <v>41.9037822</v>
       </c>
       <c r="N54">
-        <v>-23.61314480000001</v>
+        <v>-24.4037822</v>
       </c>
       <c r="O54">
-        <v>-7.083943440000002</v>
+        <v>-7.32113466</v>
       </c>
       <c r="P54">
-        <v>-16.52920136000001</v>
+        <v>-17.08264754</v>
       </c>
       <c r="Q54">
-        <v>20.47079863999999</v>
+        <v>19.91735246</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1155164536014167</v>
+        <v>0.1169997824014468</v>
       </c>
       <c r="T54">
-        <v>1.610079759847961</v>
+        <v>1.644336776014939</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1276963858040847</v>
+        <v>0.1252870200341963</v>
       </c>
       <c r="W54">
-        <v>0.2056891922273968</v>
+        <v>0.2062573206759365</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.425654619346949</v>
+        <v>0.4176234001139878</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1643062776869264</v>
+        <v>0.1662062776869264</v>
       </c>
       <c r="C55">
-        <v>-50.67271333389027</v>
+        <v>-55.39085231821656</v>
       </c>
       <c r="D55">
-        <v>96.63628666610973</v>
+        <v>95.27114768178346</v>
       </c>
       <c r="E55">
-        <v>12.90899999999999</v>
+        <v>16.262</v>
       </c>
       <c r="F55">
-        <v>177.709</v>
+        <v>181.062</v>
       </c>
       <c r="G55">
         <v>30.4</v>
@@ -5803,37 +5803,37 @@
         <v>17.5</v>
       </c>
       <c r="M55">
-        <v>41.9037822</v>
+        <v>42.6944196</v>
       </c>
       <c r="N55">
-        <v>-24.4037822</v>
+        <v>-25.1944196</v>
       </c>
       <c r="O55">
-        <v>-7.32113466</v>
+        <v>-7.558325880000001</v>
       </c>
       <c r="P55">
-        <v>-17.08264754</v>
+        <v>-17.63609372</v>
       </c>
       <c r="Q55">
-        <v>19.91735246</v>
+        <v>19.36390628</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1169997824014468</v>
+        <v>0.118547603758</v>
       </c>
       <c r="T55">
-        <v>1.644336776014939</v>
+        <v>1.680083227667437</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1252870200341963</v>
+        <v>0.1229668900335631</v>
       </c>
       <c r="W55">
-        <v>0.2062573206759365</v>
+        <v>0.2068044073300858</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4176234001139878</v>
+        <v>0.4098896334452102</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1662062776869264</v>
+        <v>0.1681062776869264</v>
       </c>
       <c r="C56">
-        <v>-55.39085231821656</v>
+        <v>-60.07095911200764</v>
       </c>
       <c r="D56">
-        <v>95.27114768178346</v>
+        <v>93.94404088799237</v>
       </c>
       <c r="E56">
-        <v>16.262</v>
+        <v>19.61500000000001</v>
       </c>
       <c r="F56">
-        <v>181.062</v>
+        <v>184.415</v>
       </c>
       <c r="G56">
         <v>30.4</v>
@@ -5885,37 +5885,37 @@
         <v>17.5</v>
       </c>
       <c r="M56">
-        <v>42.6944196</v>
+        <v>43.485057</v>
       </c>
       <c r="N56">
-        <v>-25.1944196</v>
+        <v>-25.985057</v>
       </c>
       <c r="O56">
-        <v>-7.558325880000001</v>
+        <v>-7.795517100000001</v>
       </c>
       <c r="P56">
-        <v>-17.63609372</v>
+        <v>-18.1895399</v>
       </c>
       <c r="Q56">
-        <v>19.36390628</v>
+        <v>18.8104601</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.118547603758</v>
+        <v>0.1201642171748445</v>
       </c>
       <c r="T56">
-        <v>1.680083227667437</v>
+        <v>1.717418410504491</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1229668900335631</v>
+        <v>0.1207311283965892</v>
       </c>
       <c r="W56">
-        <v>0.2068044073300858</v>
+        <v>0.2073315999240843</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4098896334452102</v>
+        <v>0.4024370946552973</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1681062776869264</v>
+        <v>0.1700062776869264</v>
       </c>
       <c r="C57">
-        <v>-60.07095911200764</v>
+        <v>-64.71460122117921</v>
       </c>
       <c r="D57">
-        <v>93.94404088799237</v>
+        <v>92.65339877882083</v>
       </c>
       <c r="E57">
-        <v>19.61500000000001</v>
+        <v>22.96800000000002</v>
       </c>
       <c r="F57">
-        <v>184.415</v>
+        <v>187.768</v>
       </c>
       <c r="G57">
         <v>30.4</v>
@@ -5967,37 +5967,37 @@
         <v>17.5</v>
       </c>
       <c r="M57">
-        <v>43.485057</v>
+        <v>44.27569440000001</v>
       </c>
       <c r="N57">
-        <v>-25.985057</v>
+        <v>-26.77569440000001</v>
       </c>
       <c r="O57">
-        <v>-7.795517100000001</v>
+        <v>-8.032708320000001</v>
       </c>
       <c r="P57">
-        <v>-18.1895399</v>
+        <v>-18.74298608</v>
       </c>
       <c r="Q57">
-        <v>18.8104601</v>
+        <v>18.25701392</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1201642171748445</v>
+        <v>0.1218543130197273</v>
       </c>
       <c r="T57">
-        <v>1.717418410504491</v>
+        <v>1.756450647106867</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1207311283965892</v>
+        <v>0.1185752153895072</v>
       </c>
       <c r="W57">
-        <v>0.2073315999240843</v>
+        <v>0.2078399642111542</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.4024370946552973</v>
+        <v>0.3952507179650241</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1700062776869264</v>
+        <v>0.1719062776869264</v>
       </c>
       <c r="C58">
-        <v>-64.71460122117921</v>
+        <v>-69.32326117885836</v>
       </c>
       <c r="D58">
-        <v>92.65339877882083</v>
+        <v>91.39773882114169</v>
       </c>
       <c r="E58">
-        <v>22.96800000000002</v>
+        <v>26.32100000000003</v>
       </c>
       <c r="F58">
-        <v>187.768</v>
+        <v>191.121</v>
       </c>
       <c r="G58">
         <v>30.4</v>
@@ -6049,37 +6049,37 @@
         <v>17.5</v>
       </c>
       <c r="M58">
-        <v>44.27569440000001</v>
+        <v>45.06633180000001</v>
       </c>
       <c r="N58">
-        <v>-26.77569440000001</v>
+        <v>-27.56633180000001</v>
       </c>
       <c r="O58">
-        <v>-8.032708320000001</v>
+        <v>-8.269899540000003</v>
       </c>
       <c r="P58">
-        <v>-18.74298608</v>
+        <v>-19.29643226</v>
       </c>
       <c r="Q58">
-        <v>18.25701392</v>
+        <v>17.70356774</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1218543130197273</v>
+        <v>0.1236230179736744</v>
       </c>
       <c r="T58">
-        <v>1.756450647106867</v>
+        <v>1.797298336574468</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1185752153895072</v>
+        <v>0.1164949484528492</v>
       </c>
       <c r="W58">
-        <v>0.2078399642111542</v>
+        <v>0.2083304911548182</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3952507179650241</v>
+        <v>0.3883164948428307</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1719062776869264</v>
+        <v>0.1738062776869264</v>
       </c>
       <c r="C59">
-        <v>-69.32326117885836</v>
+        <v>-73.8983422262485</v>
       </c>
       <c r="D59">
-        <v>91.39773882114169</v>
+        <v>90.17565777375152</v>
       </c>
       <c r="E59">
-        <v>26.32100000000003</v>
+        <v>29.67400000000001</v>
       </c>
       <c r="F59">
-        <v>191.121</v>
+        <v>194.474</v>
       </c>
       <c r="G59">
         <v>30.4</v>
@@ -6131,37 +6131,37 @@
         <v>17.5</v>
       </c>
       <c r="M59">
-        <v>45.06633180000001</v>
+        <v>45.85696920000001</v>
       </c>
       <c r="N59">
-        <v>-27.56633180000001</v>
+        <v>-28.35696920000001</v>
       </c>
       <c r="O59">
-        <v>-8.269899540000003</v>
+        <v>-8.507090760000002</v>
       </c>
       <c r="P59">
-        <v>-19.29643226</v>
+        <v>-19.84987844</v>
       </c>
       <c r="Q59">
-        <v>17.70356774</v>
+        <v>17.15012156</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1236230179736744</v>
+        <v>0.1254759469730477</v>
       </c>
       <c r="T59">
-        <v>1.797298336574468</v>
+        <v>1.840091154111955</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1164949484528492</v>
+        <v>0.1144864148588346</v>
       </c>
       <c r="W59">
-        <v>0.2083304911548182</v>
+        <v>0.2088041033762868</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3883164948428307</v>
+        <v>0.3816213828627819</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1738062776869264</v>
+        <v>0.1757062776869264</v>
       </c>
       <c r="C60">
-        <v>-73.89834222624847</v>
+        <v>-78.44117354375339</v>
       </c>
       <c r="D60">
-        <v>90.17565777375152</v>
+        <v>88.98582645624661</v>
       </c>
       <c r="E60">
-        <v>29.67399999999998</v>
+        <v>33.02699999999999</v>
       </c>
       <c r="F60">
-        <v>194.474</v>
+        <v>197.827</v>
       </c>
       <c r="G60">
         <v>30.4</v>
@@ -6213,37 +6213,37 @@
         <v>17.5</v>
       </c>
       <c r="M60">
-        <v>45.8569692</v>
+        <v>46.6476066</v>
       </c>
       <c r="N60">
-        <v>-28.3569692</v>
+        <v>-29.1476066</v>
       </c>
       <c r="O60">
-        <v>-8.507090760000001</v>
+        <v>-8.74428198</v>
       </c>
       <c r="P60">
-        <v>-19.84987844</v>
+        <v>-20.40332462</v>
       </c>
       <c r="Q60">
-        <v>17.15012156</v>
+        <v>16.59667538</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1254759469730476</v>
+        <v>0.1274192627528781</v>
       </c>
       <c r="T60">
-        <v>1.840091154111955</v>
+        <v>1.884971426163466</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1144864148588346</v>
+        <v>0.1125459671493628</v>
       </c>
       <c r="W60">
-        <v>0.2088041033762868</v>
+        <v>0.2092616609461803</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3816213828627819</v>
+        <v>0.3751532238312093</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1757062776869264</v>
+        <v>0.1776062776869264</v>
       </c>
       <c r="C61">
-        <v>-78.44117354375339</v>
+        <v>-82.95301507335924</v>
       </c>
       <c r="D61">
-        <v>88.98582645624661</v>
+        <v>87.82698492664078</v>
       </c>
       <c r="E61">
-        <v>33.02699999999999</v>
+        <v>36.38</v>
       </c>
       <c r="F61">
-        <v>197.827</v>
+        <v>201.18</v>
       </c>
       <c r="G61">
         <v>30.4</v>
@@ -6295,37 +6295,37 @@
         <v>17.5</v>
       </c>
       <c r="M61">
-        <v>46.6476066</v>
+        <v>47.438244</v>
       </c>
       <c r="N61">
-        <v>-29.1476066</v>
+        <v>-29.938244</v>
       </c>
       <c r="O61">
-        <v>-8.74428198</v>
+        <v>-8.981473200000002</v>
       </c>
       <c r="P61">
-        <v>-20.40332462</v>
+        <v>-20.9567708</v>
       </c>
       <c r="Q61">
-        <v>16.59667538</v>
+        <v>16.0432292</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1274192627528781</v>
+        <v>0.1294597443217</v>
       </c>
       <c r="T61">
-        <v>1.884971426163466</v>
+        <v>1.932095711817553</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1125459671493628</v>
+        <v>0.1106702010302067</v>
       </c>
       <c r="W61">
-        <v>0.2092616609461803</v>
+        <v>0.2097039665970773</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3751532238312093</v>
+        <v>0.3689006701006892</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1776062776869264</v>
+        <v>0.1795062776869264</v>
       </c>
       <c r="C62">
-        <v>-82.95301507335924</v>
+        <v>-87.43506196905622</v>
       </c>
       <c r="D62">
-        <v>87.82698492664078</v>
+        <v>86.69793803094379</v>
       </c>
       <c r="E62">
-        <v>36.38</v>
+        <v>39.733</v>
       </c>
       <c r="F62">
-        <v>201.18</v>
+        <v>204.533</v>
       </c>
       <c r="G62">
         <v>30.4</v>
@@ -6377,37 +6377,37 @@
         <v>17.5</v>
       </c>
       <c r="M62">
-        <v>47.438244</v>
+        <v>48.22888140000001</v>
       </c>
       <c r="N62">
-        <v>-29.938244</v>
+        <v>-30.72888140000001</v>
       </c>
       <c r="O62">
-        <v>-8.981473200000002</v>
+        <v>-9.218664420000001</v>
       </c>
       <c r="P62">
-        <v>-20.9567708</v>
+        <v>-21.51021698</v>
       </c>
       <c r="Q62">
-        <v>16.0432292</v>
+        <v>15.48978302</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1294597443217</v>
+        <v>0.1316048659709744</v>
       </c>
       <c r="T62">
-        <v>1.932095711817553</v>
+        <v>1.981636627505182</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1106702010302067</v>
+        <v>0.1088559354395476</v>
       </c>
       <c r="W62">
-        <v>0.2097039665970773</v>
+        <v>0.2101317704233547</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3689006701006892</v>
+        <v>0.3628531181318254</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1795062776869264</v>
+        <v>0.1814062776869264</v>
       </c>
       <c r="C63">
-        <v>-87.43506196905622</v>
+        <v>-91.88844870834623</v>
       </c>
       <c r="D63">
-        <v>86.69793803094379</v>
+        <v>85.59755129165377</v>
       </c>
       <c r="E63">
-        <v>39.733</v>
+        <v>43.08599999999998</v>
       </c>
       <c r="F63">
-        <v>204.533</v>
+        <v>207.886</v>
       </c>
       <c r="G63">
         <v>30.4</v>
@@ -6459,37 +6459,37 @@
         <v>17.5</v>
       </c>
       <c r="M63">
-        <v>48.22888140000001</v>
+        <v>49.0195188</v>
       </c>
       <c r="N63">
-        <v>-30.72888140000001</v>
+        <v>-31.5195188</v>
       </c>
       <c r="O63">
-        <v>-9.218664420000001</v>
+        <v>-9.455855639999999</v>
       </c>
       <c r="P63">
-        <v>-21.51021698</v>
+        <v>-22.06366316</v>
       </c>
       <c r="Q63">
-        <v>15.48978302</v>
+        <v>14.93633684</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1316048659709744</v>
+        <v>0.1338628887596842</v>
       </c>
       <c r="T63">
-        <v>1.981636627505182</v>
+        <v>2.03378495980795</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1088559354395476</v>
+        <v>0.1071001945453614</v>
       </c>
       <c r="W63">
-        <v>0.2101317704233547</v>
+        <v>0.2105457741262038</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3628531181318254</v>
+        <v>0.3570006484845379</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1814062776869264</v>
+        <v>0.1833062776869264</v>
       </c>
       <c r="C64">
-        <v>-91.88844870834623</v>
+        <v>-96.3142528945711</v>
       </c>
       <c r="D64">
-        <v>85.59755129165377</v>
+        <v>84.52474710542892</v>
       </c>
       <c r="E64">
-        <v>43.08599999999998</v>
+        <v>46.43899999999999</v>
       </c>
       <c r="F64">
-        <v>207.886</v>
+        <v>211.239</v>
       </c>
       <c r="G64">
         <v>30.4</v>
@@ -6541,37 +6541,37 @@
         <v>17.5</v>
       </c>
       <c r="M64">
-        <v>49.0195188</v>
+        <v>49.8101562</v>
       </c>
       <c r="N64">
-        <v>-31.5195188</v>
+        <v>-32.3101562</v>
       </c>
       <c r="O64">
-        <v>-9.455855639999999</v>
+        <v>-9.693046860000001</v>
       </c>
       <c r="P64">
-        <v>-22.06366316</v>
+        <v>-22.61710934</v>
       </c>
       <c r="Q64">
-        <v>14.93633684</v>
+        <v>14.38289066</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1338628887596842</v>
+        <v>0.1362429668342703</v>
       </c>
       <c r="T64">
-        <v>2.03378495980795</v>
+        <v>2.088752120883841</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1071001945453614</v>
+        <v>0.1054001914573398</v>
       </c>
       <c r="W64">
-        <v>0.2105457741262038</v>
+        <v>0.2109466348543593</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3570006484845379</v>
+        <v>0.3513339715244659</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1833062776869264</v>
+        <v>0.1852062776869264</v>
       </c>
       <c r="C65">
-        <v>-96.3142528945711</v>
+        <v>-100.7134987768491</v>
       </c>
       <c r="D65">
-        <v>84.52474710542892</v>
+        <v>83.47850122315091</v>
       </c>
       <c r="E65">
-        <v>46.43899999999999</v>
+        <v>49.792</v>
       </c>
       <c r="F65">
-        <v>211.239</v>
+        <v>214.592</v>
       </c>
       <c r="G65">
         <v>30.4</v>
@@ -6623,37 +6623,37 @@
         <v>17.5</v>
       </c>
       <c r="M65">
-        <v>49.8101562</v>
+        <v>50.6007936</v>
       </c>
       <c r="N65">
-        <v>-32.3101562</v>
+        <v>-33.1007936</v>
       </c>
       <c r="O65">
-        <v>-9.693046860000001</v>
+        <v>-9.930238080000001</v>
       </c>
       <c r="P65">
-        <v>-22.61710934</v>
+        <v>-23.17055552</v>
       </c>
       <c r="Q65">
-        <v>14.38289066</v>
+        <v>13.82944448</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1362429668342703</v>
+        <v>0.1387552714685556</v>
       </c>
       <c r="T65">
-        <v>2.088752120883841</v>
+        <v>2.146773013130614</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1054001914573398</v>
+        <v>0.1037533134658188</v>
       </c>
       <c r="W65">
-        <v>0.2109466348543593</v>
+        <v>0.2113349686847599</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3513339715244659</v>
+        <v>0.3458443782193962</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1852062776869264</v>
+        <v>0.1871062776869264</v>
       </c>
       <c r="C66">
-        <v>-100.7134987768491</v>
+        <v>-105.0871605117902</v>
       </c>
       <c r="D66">
-        <v>83.47850122315091</v>
+        <v>82.45783948820986</v>
       </c>
       <c r="E66">
-        <v>49.792</v>
+        <v>53.14500000000001</v>
       </c>
       <c r="F66">
-        <v>214.592</v>
+        <v>217.945</v>
       </c>
       <c r="G66">
         <v>30.4</v>
@@ -6705,37 +6705,37 @@
         <v>17.5</v>
       </c>
       <c r="M66">
-        <v>50.6007936</v>
+        <v>51.391431</v>
       </c>
       <c r="N66">
-        <v>-33.1007936</v>
+        <v>-33.891431</v>
       </c>
       <c r="O66">
-        <v>-9.930238080000001</v>
+        <v>-10.1674293</v>
       </c>
       <c r="P66">
-        <v>-23.17055552</v>
+        <v>-23.7240017</v>
       </c>
       <c r="Q66">
-        <v>13.82944448</v>
+        <v>13.2759983</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1387552714685556</v>
+        <v>0.1414111363676572</v>
       </c>
       <c r="T66">
-        <v>2.146773013130614</v>
+        <v>2.208109384934346</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1037533134658188</v>
+        <v>0.1021571086432678</v>
       </c>
       <c r="W66">
-        <v>0.2113349686847599</v>
+        <v>0.2117113537819175</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3458443782193962</v>
+        <v>0.3405236954775592</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1871062776869264</v>
+        <v>0.1890062776869263</v>
       </c>
       <c r="C67">
-        <v>-105.0871605117902</v>
+        <v>-109.4361651888219</v>
       </c>
       <c r="D67">
-        <v>82.45783948820986</v>
+        <v>81.46183481117815</v>
       </c>
       <c r="E67">
-        <v>53.14500000000001</v>
+        <v>56.49800000000002</v>
       </c>
       <c r="F67">
-        <v>217.945</v>
+        <v>221.298</v>
       </c>
       <c r="G67">
         <v>30.4</v>
@@ -6787,37 +6787,37 @@
         <v>17.5</v>
       </c>
       <c r="M67">
-        <v>51.391431</v>
+        <v>52.18206840000001</v>
       </c>
       <c r="N67">
-        <v>-33.891431</v>
+        <v>-34.68206840000001</v>
       </c>
       <c r="O67">
-        <v>-10.1674293</v>
+        <v>-10.40462052</v>
       </c>
       <c r="P67">
-        <v>-23.7240017</v>
+        <v>-24.27744788000001</v>
       </c>
       <c r="Q67">
-        <v>13.2759983</v>
+        <v>12.72255211999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1414111363676572</v>
+        <v>0.1442232286137647</v>
       </c>
       <c r="T67">
-        <v>2.208109384934346</v>
+        <v>2.273053778608885</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1021571086432678</v>
+        <v>0.1006092736638243</v>
       </c>
       <c r="W67">
-        <v>0.2117113537819175</v>
+        <v>0.2120763332700702</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3405236954775592</v>
+        <v>0.335364245546081</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1890062776869263</v>
+        <v>0.1909062776869264</v>
       </c>
       <c r="C68">
-        <v>-109.4361651888219</v>
+        <v>-113.761395638876</v>
       </c>
       <c r="D68">
-        <v>81.46183481117815</v>
+        <v>80.48960436112401</v>
       </c>
       <c r="E68">
-        <v>56.49800000000002</v>
+        <v>59.851</v>
       </c>
       <c r="F68">
-        <v>221.298</v>
+        <v>224.651</v>
       </c>
       <c r="G68">
         <v>30.4</v>
@@ -6869,37 +6869,37 @@
         <v>17.5</v>
       </c>
       <c r="M68">
-        <v>52.18206840000001</v>
+        <v>52.97270580000001</v>
       </c>
       <c r="N68">
-        <v>-34.68206840000001</v>
+        <v>-35.47270580000001</v>
       </c>
       <c r="O68">
-        <v>-10.40462052</v>
+        <v>-10.64181174</v>
       </c>
       <c r="P68">
-        <v>-24.27744788000001</v>
+        <v>-24.83089406000001</v>
       </c>
       <c r="Q68">
-        <v>12.72255211999999</v>
+        <v>12.16910593999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1442232286137647</v>
+        <v>0.1472057506929698</v>
       </c>
       <c r="T68">
-        <v>2.273053778608885</v>
+        <v>2.341934196142489</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1006092736638243</v>
+        <v>0.09910764271361798</v>
       </c>
       <c r="W68">
-        <v>0.2120763332700702</v>
+        <v>0.2124304178481289</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.335364245546081</v>
+        <v>0.3303588090453933</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1909062776869264</v>
+        <v>0.1928062776869264</v>
       </c>
       <c r="C69">
-        <v>-113.761395638876</v>
+        <v>-118.06369304432</v>
       </c>
       <c r="D69">
-        <v>80.48960436112401</v>
+        <v>79.54030695567997</v>
       </c>
       <c r="E69">
-        <v>59.851</v>
+        <v>63.20400000000001</v>
       </c>
       <c r="F69">
-        <v>224.651</v>
+        <v>228.004</v>
       </c>
       <c r="G69">
         <v>30.4</v>
@@ -6951,37 +6951,37 @@
         <v>17.5</v>
       </c>
       <c r="M69">
-        <v>52.97270580000001</v>
+        <v>53.76334320000001</v>
       </c>
       <c r="N69">
-        <v>-35.47270580000001</v>
+        <v>-36.26334320000001</v>
       </c>
       <c r="O69">
-        <v>-10.64181174</v>
+        <v>-10.87900296</v>
       </c>
       <c r="P69">
-        <v>-24.83089406000001</v>
+        <v>-25.38434024000001</v>
       </c>
       <c r="Q69">
-        <v>12.16910593999999</v>
+        <v>11.61565975999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1472057506929698</v>
+        <v>0.1503746804021251</v>
       </c>
       <c r="T69">
-        <v>2.341934196142489</v>
+        <v>2.415119639771941</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09910764271361798</v>
+        <v>0.09765017737959418</v>
       </c>
       <c r="W69">
-        <v>0.2124304178481289</v>
+        <v>0.2127740881738917</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3303588090453933</v>
+        <v>0.3255005912653139</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1928062776869264</v>
+        <v>0.1947062776869264</v>
       </c>
       <c r="C70">
-        <v>-118.06369304432</v>
+        <v>-122.3438593663523</v>
       </c>
       <c r="D70">
-        <v>79.54030695567997</v>
+        <v>78.61314063364773</v>
       </c>
       <c r="E70">
-        <v>63.20400000000001</v>
+        <v>66.55700000000002</v>
       </c>
       <c r="F70">
-        <v>228.004</v>
+        <v>231.357</v>
       </c>
       <c r="G70">
         <v>30.4</v>
@@ -7033,37 +7033,37 @@
         <v>17.5</v>
       </c>
       <c r="M70">
-        <v>53.76334320000001</v>
+        <v>54.55398060000001</v>
       </c>
       <c r="N70">
-        <v>-36.26334320000001</v>
+        <v>-37.05398060000001</v>
       </c>
       <c r="O70">
-        <v>-10.87900296</v>
+        <v>-11.11619418</v>
       </c>
       <c r="P70">
-        <v>-25.38434024000001</v>
+        <v>-25.93778642000001</v>
       </c>
       <c r="Q70">
-        <v>11.61565975999999</v>
+        <v>11.06221357999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1503746804021251</v>
+        <v>0.1537480571892904</v>
       </c>
       <c r="T70">
-        <v>2.415119639771941</v>
+        <v>2.493026724925875</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09765017737959418</v>
+        <v>0.09623495741757107</v>
       </c>
       <c r="W70">
-        <v>0.2127740881738917</v>
+        <v>0.2131077970409368</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3255005912653139</v>
+        <v>0.3207831913919036</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1947062776869264</v>
+        <v>0.1966062776869264</v>
       </c>
       <c r="C71">
-        <v>-122.3438593663523</v>
+        <v>-126.602659604582</v>
       </c>
       <c r="D71">
-        <v>78.61314063364773</v>
+        <v>77.70734039541799</v>
       </c>
       <c r="E71">
-        <v>66.55700000000002</v>
+        <v>69.91000000000003</v>
       </c>
       <c r="F71">
-        <v>231.357</v>
+        <v>234.71</v>
       </c>
       <c r="G71">
         <v>30.4</v>
@@ -7115,37 +7115,37 @@
         <v>17.5</v>
       </c>
       <c r="M71">
-        <v>54.55398060000001</v>
+        <v>55.34461800000001</v>
       </c>
       <c r="N71">
-        <v>-37.05398060000001</v>
+        <v>-37.84461800000001</v>
       </c>
       <c r="O71">
-        <v>-11.11619418</v>
+        <v>-11.3533854</v>
       </c>
       <c r="P71">
-        <v>-25.93778642000001</v>
+        <v>-26.49123260000001</v>
       </c>
       <c r="Q71">
-        <v>11.06221357999999</v>
+        <v>10.50876739999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1537480571892904</v>
+        <v>0.1573463257622667</v>
       </c>
       <c r="T71">
-        <v>2.493026724925875</v>
+        <v>2.576127615756738</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09623495741757107</v>
+        <v>0.09486017231160578</v>
       </c>
       <c r="W71">
-        <v>0.2131077970409368</v>
+        <v>0.2134319713689234</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3207831913919036</v>
+        <v>0.3162005743720193</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1966062776869264</v>
+        <v>0.1985062776869264</v>
       </c>
       <c r="C72">
-        <v>-126.602659604582</v>
+        <v>-130.8408239021773</v>
       </c>
       <c r="D72">
-        <v>77.70734039541799</v>
+        <v>76.82217609782275</v>
       </c>
       <c r="E72">
-        <v>69.91000000000003</v>
+        <v>73.26300000000003</v>
       </c>
       <c r="F72">
-        <v>234.71</v>
+        <v>238.063</v>
       </c>
       <c r="G72">
         <v>30.4</v>
@@ -7197,37 +7197,37 @@
         <v>17.5</v>
       </c>
       <c r="M72">
-        <v>55.34461800000001</v>
+        <v>56.13525540000001</v>
       </c>
       <c r="N72">
-        <v>-37.84461800000001</v>
+        <v>-38.63525540000001</v>
       </c>
       <c r="O72">
-        <v>-11.3533854</v>
+        <v>-11.59057662</v>
       </c>
       <c r="P72">
-        <v>-26.49123260000001</v>
+        <v>-27.04467878000001</v>
       </c>
       <c r="Q72">
-        <v>10.50876739999999</v>
+        <v>9.955321219999991</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1573463257622667</v>
+        <v>0.1611927507885518</v>
       </c>
       <c r="T72">
-        <v>2.576127615756738</v>
+        <v>2.66495960250697</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09486017231160578</v>
+        <v>0.09352411354665358</v>
       </c>
       <c r="W72">
-        <v>0.2134319713689234</v>
+        <v>0.2137470140256991</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3162005743720193</v>
+        <v>0.311747045155512</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1985062776869264</v>
+        <v>0.2004062776869264</v>
       </c>
       <c r="C73">
-        <v>-130.8408239021772</v>
+        <v>-135.0590495087536</v>
       </c>
       <c r="D73">
-        <v>76.82217609782275</v>
+        <v>75.95695049124642</v>
       </c>
       <c r="E73">
-        <v>73.26299999999998</v>
+        <v>76.61599999999999</v>
       </c>
       <c r="F73">
-        <v>238.063</v>
+        <v>241.416</v>
       </c>
       <c r="G73">
         <v>30.4</v>
@@ -7279,37 +7279,37 @@
         <v>17.5</v>
       </c>
       <c r="M73">
-        <v>56.1352554</v>
+        <v>56.9258928</v>
       </c>
       <c r="N73">
-        <v>-38.6352554</v>
+        <v>-39.4258928</v>
       </c>
       <c r="O73">
-        <v>-11.59057662</v>
+        <v>-11.82776784</v>
       </c>
       <c r="P73">
-        <v>-27.04467878</v>
+        <v>-27.59812496</v>
       </c>
       <c r="Q73">
-        <v>9.955321220000002</v>
+        <v>9.40187504</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1611927507885518</v>
+        <v>0.1653139204595715</v>
       </c>
       <c r="T73">
-        <v>2.664959602506969</v>
+        <v>2.760136731167932</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09352411354665362</v>
+        <v>0.09222516752517231</v>
       </c>
       <c r="W73">
-        <v>0.2137470140256991</v>
+        <v>0.2140533054975644</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.311747045155512</v>
+        <v>0.3074172250839077</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2004062776869264</v>
+        <v>0.2023062776869264</v>
       </c>
       <c r="C74">
-        <v>-135.0590495087536</v>
+        <v>-139.2580026120964</v>
       </c>
       <c r="D74">
-        <v>75.95695049124642</v>
+        <v>75.11099738790358</v>
       </c>
       <c r="E74">
-        <v>76.61599999999999</v>
+        <v>79.96899999999999</v>
       </c>
       <c r="F74">
-        <v>241.416</v>
+        <v>244.769</v>
       </c>
       <c r="G74">
         <v>30.4</v>
@@ -7361,37 +7361,37 @@
         <v>17.5</v>
       </c>
       <c r="M74">
-        <v>56.9258928</v>
+        <v>57.7165302</v>
       </c>
       <c r="N74">
-        <v>-39.4258928</v>
+        <v>-40.2165302</v>
       </c>
       <c r="O74">
-        <v>-11.82776784</v>
+        <v>-12.06495906</v>
       </c>
       <c r="P74">
-        <v>-27.59812496</v>
+        <v>-28.15157114</v>
       </c>
       <c r="Q74">
-        <v>9.40187504</v>
+        <v>8.848428859999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1653139204595715</v>
+        <v>0.1697403619580741</v>
       </c>
       <c r="T74">
-        <v>2.760136731167932</v>
+        <v>2.862364017507485</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09222516752517231</v>
+        <v>0.09096180906592337</v>
       </c>
       <c r="W74">
-        <v>0.2140533054975644</v>
+        <v>0.2143512054222553</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3074172250839077</v>
+        <v>0.3032060302197446</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2023062776869264</v>
+        <v>0.2042062776869263</v>
       </c>
       <c r="C75">
-        <v>-139.2580026120964</v>
+        <v>-143.4383200488287</v>
       </c>
       <c r="D75">
-        <v>75.11099738790358</v>
+        <v>74.28367995117131</v>
       </c>
       <c r="E75">
-        <v>79.96899999999999</v>
+        <v>83.322</v>
       </c>
       <c r="F75">
-        <v>244.769</v>
+        <v>248.122</v>
       </c>
       <c r="G75">
         <v>30.4</v>
@@ -7443,37 +7443,37 @@
         <v>17.5</v>
       </c>
       <c r="M75">
-        <v>57.7165302</v>
+        <v>58.5071676</v>
       </c>
       <c r="N75">
-        <v>-40.2165302</v>
+        <v>-41.0071676</v>
       </c>
       <c r="O75">
-        <v>-12.06495906</v>
+        <v>-12.30215028</v>
       </c>
       <c r="P75">
-        <v>-28.15157114</v>
+        <v>-28.70501732</v>
       </c>
       <c r="Q75">
-        <v>8.848428859999999</v>
+        <v>8.294982679999997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1697403619580741</v>
+        <v>0.1745072989564616</v>
       </c>
       <c r="T75">
-        <v>2.862364017507485</v>
+        <v>2.972454941257773</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09096180906592337</v>
+        <v>0.08973259542989738</v>
       </c>
       <c r="W75">
-        <v>0.2143512054222553</v>
+        <v>0.2146410539976302</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3032060302197446</v>
+        <v>0.2991086514329913</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2042062776869263</v>
+        <v>0.2061062776869264</v>
       </c>
       <c r="C76">
-        <v>-143.4383200488287</v>
+        <v>-147.6006109032566</v>
       </c>
       <c r="D76">
-        <v>74.28367995117131</v>
+        <v>73.47438909674339</v>
       </c>
       <c r="E76">
-        <v>83.322</v>
+        <v>86.67500000000001</v>
       </c>
       <c r="F76">
-        <v>248.122</v>
+        <v>251.475</v>
       </c>
       <c r="G76">
         <v>30.4</v>
@@ -7525,37 +7525,37 @@
         <v>17.5</v>
       </c>
       <c r="M76">
-        <v>58.5071676</v>
+        <v>59.29780500000001</v>
       </c>
       <c r="N76">
-        <v>-41.0071676</v>
+        <v>-41.79780500000001</v>
       </c>
       <c r="O76">
-        <v>-12.30215028</v>
+        <v>-12.5393415</v>
       </c>
       <c r="P76">
-        <v>-28.70501732</v>
+        <v>-29.25846350000001</v>
       </c>
       <c r="Q76">
-        <v>8.294982679999997</v>
+        <v>7.741536499999992</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1745072989564616</v>
+        <v>0.1796555909147201</v>
       </c>
       <c r="T76">
-        <v>2.972454941257773</v>
+        <v>3.091353138908084</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08973259542989738</v>
+        <v>0.08853616082416539</v>
       </c>
       <c r="W76">
-        <v>0.2146410539976302</v>
+        <v>0.2149231732776618</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2991086514329913</v>
+        <v>0.2951205360805513</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2061062776869264</v>
+        <v>0.2080062776869264</v>
       </c>
       <c r="C77">
-        <v>-147.6006109032566</v>
+        <v>-151.7454580028288</v>
       </c>
       <c r="D77">
-        <v>73.47438909674339</v>
+        <v>72.68254199717123</v>
       </c>
       <c r="E77">
-        <v>86.67500000000001</v>
+        <v>90.02799999999999</v>
       </c>
       <c r="F77">
-        <v>251.475</v>
+        <v>254.828</v>
       </c>
       <c r="G77">
         <v>30.4</v>
@@ -7607,37 +7607,37 @@
         <v>17.5</v>
       </c>
       <c r="M77">
-        <v>59.29780500000001</v>
+        <v>60.08844240000001</v>
       </c>
       <c r="N77">
-        <v>-41.79780500000001</v>
+        <v>-42.58844240000001</v>
       </c>
       <c r="O77">
-        <v>-12.5393415</v>
+        <v>-12.77653272</v>
       </c>
       <c r="P77">
-        <v>-29.25846350000001</v>
+        <v>-29.81190968000001</v>
       </c>
       <c r="Q77">
-        <v>7.741536499999992</v>
+        <v>7.188090319999993</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1796555909147201</v>
+        <v>0.1852329072028334</v>
       </c>
       <c r="T77">
-        <v>3.091353138908084</v>
+        <v>3.220159519695922</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08853616082416539</v>
+        <v>0.08737121133963692</v>
       </c>
       <c r="W77">
-        <v>0.2149231732776618</v>
+        <v>0.2151978683661136</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2951205360805513</v>
+        <v>0.291237371132123</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2080062776869264</v>
+        <v>0.2099062776869264</v>
       </c>
       <c r="C78">
-        <v>-151.7454580028288</v>
+        <v>-155.8734193179257</v>
       </c>
       <c r="D78">
-        <v>72.68254199717123</v>
+        <v>71.90758068207435</v>
       </c>
       <c r="E78">
-        <v>90.02799999999999</v>
+        <v>93.38100000000003</v>
       </c>
       <c r="F78">
-        <v>254.828</v>
+        <v>258.181</v>
       </c>
       <c r="G78">
         <v>30.4</v>
@@ -7689,37 +7689,37 @@
         <v>17.5</v>
       </c>
       <c r="M78">
-        <v>60.08844240000001</v>
+        <v>60.87907980000001</v>
       </c>
       <c r="N78">
-        <v>-42.58844240000001</v>
+        <v>-43.37907980000001</v>
       </c>
       <c r="O78">
-        <v>-12.77653272</v>
+        <v>-13.01372394</v>
       </c>
       <c r="P78">
-        <v>-29.81190968000001</v>
+        <v>-30.36535586000001</v>
       </c>
       <c r="Q78">
-        <v>7.188090319999993</v>
+        <v>6.634644139999992</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1852329072028334</v>
+        <v>0.1912952075160001</v>
       </c>
       <c r="T78">
-        <v>3.220159519695922</v>
+        <v>3.360166455334875</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08737121133963692</v>
+        <v>0.08623652028327798</v>
       </c>
       <c r="W78">
-        <v>0.2151978683661136</v>
+        <v>0.215465428517203</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.291237371132123</v>
+        <v>0.2874550676109267</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2099062776869264</v>
+        <v>0.2118062776869264</v>
       </c>
       <c r="C79">
-        <v>-155.8734193179257</v>
+        <v>-159.9850292730439</v>
       </c>
       <c r="D79">
-        <v>71.90758068207435</v>
+        <v>71.14897072695611</v>
       </c>
       <c r="E79">
-        <v>93.38100000000003</v>
+        <v>96.73399999999998</v>
       </c>
       <c r="F79">
-        <v>258.181</v>
+        <v>261.534</v>
       </c>
       <c r="G79">
         <v>30.4</v>
@@ -7771,37 +7771,37 @@
         <v>17.5</v>
       </c>
       <c r="M79">
-        <v>60.87907980000001</v>
+        <v>61.6697172</v>
       </c>
       <c r="N79">
-        <v>-43.37907980000001</v>
+        <v>-44.1697172</v>
       </c>
       <c r="O79">
-        <v>-13.01372394</v>
+        <v>-13.25091516</v>
       </c>
       <c r="P79">
-        <v>-30.36535586000001</v>
+        <v>-30.91880204</v>
       </c>
       <c r="Q79">
-        <v>6.634644139999992</v>
+        <v>6.081197959999997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1912952075160001</v>
+        <v>0.1979086260394546</v>
       </c>
       <c r="T79">
-        <v>3.360166455334875</v>
+        <v>3.512901294213733</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08623652028327798</v>
+        <v>0.08513092386938982</v>
       </c>
       <c r="W79">
-        <v>0.215465428517203</v>
+        <v>0.2157261281515979</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2874550676109267</v>
+        <v>0.2837697462312994</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2118062776869264</v>
+        <v>0.2137062776869264</v>
       </c>
       <c r="C80">
-        <v>-159.9850292730439</v>
+        <v>-164.0807999758507</v>
       </c>
       <c r="D80">
-        <v>71.14897072695611</v>
+        <v>70.40620002414929</v>
       </c>
       <c r="E80">
-        <v>96.73399999999998</v>
+        <v>100.087</v>
       </c>
       <c r="F80">
-        <v>261.534</v>
+        <v>264.887</v>
       </c>
       <c r="G80">
         <v>30.4</v>
@@ -7853,37 +7853,37 @@
         <v>17.5</v>
       </c>
       <c r="M80">
-        <v>61.6697172</v>
+        <v>62.4603546</v>
       </c>
       <c r="N80">
-        <v>-44.1697172</v>
+        <v>-44.9603546</v>
       </c>
       <c r="O80">
-        <v>-13.25091516</v>
+        <v>-13.48810638</v>
       </c>
       <c r="P80">
-        <v>-30.91880204</v>
+        <v>-31.47224822</v>
       </c>
       <c r="Q80">
-        <v>6.081197959999997</v>
+        <v>5.527751779999996</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1979086260394546</v>
+        <v>0.2051518939460953</v>
       </c>
       <c r="T80">
-        <v>3.512901294213733</v>
+        <v>3.680182308223911</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08513092386938982</v>
+        <v>0.08405331723813171</v>
       </c>
       <c r="W80">
-        <v>0.2157261281515979</v>
+        <v>0.2159802277952486</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2837697462312994</v>
+        <v>0.2801777241271057</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2137062776869264</v>
+        <v>0.2156062776869264</v>
       </c>
       <c r="C81">
-        <v>-164.0807999758507</v>
+        <v>-168.1612223700486</v>
       </c>
       <c r="D81">
-        <v>70.40620002414929</v>
+        <v>69.67877762995136</v>
       </c>
       <c r="E81">
-        <v>100.087</v>
+        <v>103.44</v>
       </c>
       <c r="F81">
-        <v>264.887</v>
+        <v>268.24</v>
       </c>
       <c r="G81">
         <v>30.4</v>
@@ -7935,37 +7935,37 @@
         <v>17.5</v>
       </c>
       <c r="M81">
-        <v>62.4603546</v>
+        <v>63.250992</v>
       </c>
       <c r="N81">
-        <v>-44.9603546</v>
+        <v>-45.750992</v>
       </c>
       <c r="O81">
-        <v>-13.48810638</v>
+        <v>-13.7252976</v>
       </c>
       <c r="P81">
-        <v>-31.47224822</v>
+        <v>-32.02569440000001</v>
       </c>
       <c r="Q81">
-        <v>5.527751779999996</v>
+        <v>4.974305599999994</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2051518939460953</v>
+        <v>0.2131194886434001</v>
       </c>
       <c r="T81">
-        <v>3.680182308223911</v>
+        <v>3.864191423635106</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08405331723813171</v>
+        <v>0.08300265077265508</v>
       </c>
       <c r="W81">
-        <v>0.2159802277952486</v>
+        <v>0.2162279749478079</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2801777241271057</v>
+        <v>0.2766755025755169</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2156062776869264</v>
+        <v>0.2175062776869264</v>
       </c>
       <c r="C82">
-        <v>-168.1612223700486</v>
+        <v>-172.2267673175037</v>
       </c>
       <c r="D82">
-        <v>69.67877762995136</v>
+        <v>68.96623268249635</v>
       </c>
       <c r="E82">
-        <v>103.44</v>
+        <v>106.793</v>
       </c>
       <c r="F82">
-        <v>268.24</v>
+        <v>271.593</v>
       </c>
       <c r="G82">
         <v>30.4</v>
@@ -8017,37 +8017,37 @@
         <v>17.5</v>
       </c>
       <c r="M82">
-        <v>63.250992</v>
+        <v>64.04162940000001</v>
       </c>
       <c r="N82">
-        <v>-45.750992</v>
+        <v>-46.54162940000001</v>
       </c>
       <c r="O82">
-        <v>-13.7252976</v>
+        <v>-13.96248882</v>
       </c>
       <c r="P82">
-        <v>-32.02569440000001</v>
+        <v>-32.57914058</v>
       </c>
       <c r="Q82">
-        <v>4.974305599999994</v>
+        <v>4.420859419999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2131194886434001</v>
+        <v>0.2219257775193686</v>
       </c>
       <c r="T82">
-        <v>3.864191423635106</v>
+        <v>4.067569919615902</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08300265077265508</v>
+        <v>0.08197792668904204</v>
       </c>
       <c r="W82">
-        <v>0.2162279749478079</v>
+        <v>0.2164696048867239</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2766755025755169</v>
+        <v>0.2732597556301402</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2175062776869264</v>
+        <v>0.2194062776869264</v>
       </c>
       <c r="C83">
-        <v>-172.2267673175037</v>
+        <v>-176.2778866146497</v>
       </c>
       <c r="D83">
-        <v>68.96623268249635</v>
+        <v>68.26811338535035</v>
       </c>
       <c r="E83">
-        <v>106.793</v>
+        <v>110.146</v>
       </c>
       <c r="F83">
-        <v>271.593</v>
+        <v>274.946</v>
       </c>
       <c r="G83">
         <v>30.4</v>
@@ -8099,37 +8099,37 @@
         <v>17.5</v>
       </c>
       <c r="M83">
-        <v>64.04162940000001</v>
+        <v>64.83226680000001</v>
       </c>
       <c r="N83">
-        <v>-46.54162940000001</v>
+        <v>-47.33226680000001</v>
       </c>
       <c r="O83">
-        <v>-13.96248882</v>
+        <v>-14.19968004</v>
       </c>
       <c r="P83">
-        <v>-32.57914058</v>
+        <v>-33.13258676000001</v>
       </c>
       <c r="Q83">
-        <v>4.420859419999999</v>
+        <v>3.867413239999991</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2219257775193686</v>
+        <v>0.2317105429371112</v>
       </c>
       <c r="T83">
-        <v>4.067569919615902</v>
+        <v>4.293546026261229</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08197792668904204</v>
+        <v>0.08097819587576104</v>
       </c>
       <c r="W83">
-        <v>0.2164696048867239</v>
+        <v>0.2167053414124956</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2732597556301402</v>
+        <v>0.2699273195858701</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2194062776869264</v>
+        <v>0.2213062776869264</v>
       </c>
       <c r="C84">
-        <v>-176.2778866146497</v>
+        <v>-180.3150139477797</v>
       </c>
       <c r="D84">
-        <v>68.26811338535035</v>
+        <v>67.5839860522203</v>
       </c>
       <c r="E84">
-        <v>110.146</v>
+        <v>113.499</v>
       </c>
       <c r="F84">
-        <v>274.946</v>
+        <v>278.299</v>
       </c>
       <c r="G84">
         <v>30.4</v>
@@ -8181,37 +8181,37 @@
         <v>17.5</v>
       </c>
       <c r="M84">
-        <v>64.83226680000001</v>
+        <v>65.62290420000001</v>
       </c>
       <c r="N84">
-        <v>-47.33226680000001</v>
+        <v>-48.12290420000001</v>
       </c>
       <c r="O84">
-        <v>-14.19968004</v>
+        <v>-14.43687126</v>
       </c>
       <c r="P84">
-        <v>-33.13258676000001</v>
+        <v>-33.68603294</v>
       </c>
       <c r="Q84">
-        <v>3.867413239999991</v>
+        <v>3.313967059999996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2317105429371112</v>
+        <v>0.2426464572275296</v>
       </c>
       <c r="T84">
-        <v>4.293546026261229</v>
+        <v>4.546107557217773</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08097819587576104</v>
+        <v>0.08000255496159524</v>
       </c>
       <c r="W84">
-        <v>0.2167053414124956</v>
+        <v>0.2169353975400558</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2699273195858701</v>
+        <v>0.2666751832053175</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2213062776869264</v>
+        <v>0.2232062776869264</v>
       </c>
       <c r="C85">
-        <v>-180.3150139477797</v>
+        <v>-184.3385657914679</v>
       </c>
       <c r="D85">
-        <v>67.5839860522203</v>
+        <v>66.91343420853218</v>
       </c>
       <c r="E85">
-        <v>113.499</v>
+        <v>116.852</v>
       </c>
       <c r="F85">
-        <v>278.299</v>
+        <v>281.652</v>
       </c>
       <c r="G85">
         <v>30.4</v>
@@ -8263,37 +8263,37 @@
         <v>17.5</v>
       </c>
       <c r="M85">
-        <v>65.62290420000001</v>
+        <v>66.41354160000002</v>
       </c>
       <c r="N85">
-        <v>-48.12290420000001</v>
+        <v>-48.91354160000002</v>
       </c>
       <c r="O85">
-        <v>-14.43687126</v>
+        <v>-14.67406248</v>
       </c>
       <c r="P85">
-        <v>-33.68603294</v>
+        <v>-34.23947912000001</v>
       </c>
       <c r="Q85">
-        <v>3.313967059999996</v>
+        <v>2.760520879999987</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2426464572275296</v>
+        <v>0.2549493608042502</v>
       </c>
       <c r="T85">
-        <v>4.546107557217773</v>
+        <v>4.830239279543885</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08000255496159524</v>
+        <v>0.0790501435930048</v>
       </c>
       <c r="W85">
-        <v>0.2169353975400558</v>
+        <v>0.2171599761407695</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2666751832053175</v>
+        <v>0.2635004786433494</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2232062776869264</v>
+        <v>0.2251062776869264</v>
       </c>
       <c r="C86">
-        <v>-184.3385657914678</v>
+        <v>-188.348942254033</v>
       </c>
       <c r="D86">
-        <v>66.91343420853218</v>
+        <v>66.256057745967</v>
       </c>
       <c r="E86">
-        <v>116.852</v>
+        <v>120.205</v>
       </c>
       <c r="F86">
-        <v>281.652</v>
+        <v>285.005</v>
       </c>
       <c r="G86">
         <v>30.4</v>
@@ -8345,37 +8345,37 @@
         <v>17.5</v>
       </c>
       <c r="M86">
-        <v>66.4135416</v>
+        <v>67.204179</v>
       </c>
       <c r="N86">
-        <v>-48.9135416</v>
+        <v>-49.704179</v>
       </c>
       <c r="O86">
-        <v>-14.67406248</v>
+        <v>-14.9112537</v>
       </c>
       <c r="P86">
-        <v>-34.23947912</v>
+        <v>-34.7929253</v>
       </c>
       <c r="Q86">
-        <v>2.760520880000001</v>
+        <v>2.2070747</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.25494936080425</v>
+        <v>0.2688926515245334</v>
       </c>
       <c r="T86">
-        <v>4.830239279543881</v>
+        <v>5.152255231513474</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07905014359300482</v>
+        <v>0.07812014190367536</v>
       </c>
       <c r="W86">
-        <v>0.2171599761407695</v>
+        <v>0.2173792705391134</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2635004786433495</v>
+        <v>0.2604004730122512</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2251062776869264</v>
+        <v>0.2270062776869263</v>
       </c>
       <c r="C87">
-        <v>-188.348942254033</v>
+        <v>-192.3465278736516</v>
       </c>
       <c r="D87">
-        <v>66.256057745967</v>
+        <v>65.6114721263484</v>
       </c>
       <c r="E87">
-        <v>120.205</v>
+        <v>123.558</v>
       </c>
       <c r="F87">
-        <v>285.005</v>
+        <v>288.358</v>
       </c>
       <c r="G87">
         <v>30.4</v>
@@ -8427,37 +8427,37 @@
         <v>17.5</v>
       </c>
       <c r="M87">
-        <v>67.204179</v>
+        <v>67.9948164</v>
       </c>
       <c r="N87">
-        <v>-49.704179</v>
+        <v>-50.4948164</v>
       </c>
       <c r="O87">
-        <v>-14.9112537</v>
+        <v>-15.14844492</v>
       </c>
       <c r="P87">
-        <v>-34.7929253</v>
+        <v>-35.34637148</v>
       </c>
       <c r="Q87">
-        <v>2.2070747</v>
+        <v>1.653628519999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2688926515245334</v>
+        <v>0.2848278409191429</v>
       </c>
       <c r="T87">
-        <v>5.152255231513474</v>
+        <v>5.520273462335864</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07812014190367536</v>
+        <v>0.07721176816060936</v>
       </c>
       <c r="W87">
-        <v>0.2173792705391134</v>
+        <v>0.2175934650677283</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2604004730122512</v>
+        <v>0.2573725605353645</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2270062776869263</v>
+        <v>0.2289062776869264</v>
       </c>
       <c r="C88">
-        <v>-192.3465278736516</v>
+        <v>-196.3316923684464</v>
       </c>
       <c r="D88">
-        <v>65.6114721263484</v>
+        <v>64.97930763155365</v>
       </c>
       <c r="E88">
-        <v>123.558</v>
+        <v>126.911</v>
       </c>
       <c r="F88">
-        <v>288.358</v>
+        <v>291.711</v>
       </c>
       <c r="G88">
         <v>30.4</v>
@@ -8509,37 +8509,37 @@
         <v>17.5</v>
       </c>
       <c r="M88">
-        <v>67.9948164</v>
+        <v>68.7854538</v>
       </c>
       <c r="N88">
-        <v>-50.4948164</v>
+        <v>-51.2854538</v>
       </c>
       <c r="O88">
-        <v>-15.14844492</v>
+        <v>-15.38563614</v>
       </c>
       <c r="P88">
-        <v>-35.34637148</v>
+        <v>-35.89981766</v>
       </c>
       <c r="Q88">
-        <v>1.653628519999998</v>
+        <v>1.100182340000003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2848278409191429</v>
+        <v>0.3032145979129232</v>
       </c>
       <c r="T88">
-        <v>5.520273462335864</v>
+        <v>5.944909882515546</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07721176816060936</v>
+        <v>0.07632427657255639</v>
       </c>
       <c r="W88">
-        <v>0.2175934650677283</v>
+        <v>0.2178027355841912</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2573725605353645</v>
+        <v>0.2544142552418547</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2289062776869264</v>
+        <v>0.2308062776869264</v>
       </c>
       <c r="C89">
-        <v>-196.3316923684464</v>
+        <v>-200.3047913436271</v>
       </c>
       <c r="D89">
-        <v>64.97930763155365</v>
+        <v>64.35920865637293</v>
       </c>
       <c r="E89">
-        <v>126.911</v>
+        <v>130.264</v>
       </c>
       <c r="F89">
-        <v>291.711</v>
+        <v>295.064</v>
       </c>
       <c r="G89">
         <v>30.4</v>
@@ -8591,37 +8591,37 @@
         <v>17.5</v>
       </c>
       <c r="M89">
-        <v>68.7854538</v>
+        <v>69.57609120000001</v>
       </c>
       <c r="N89">
-        <v>-51.2854538</v>
+        <v>-52.07609120000001</v>
       </c>
       <c r="O89">
-        <v>-15.38563614</v>
+        <v>-15.62282736</v>
       </c>
       <c r="P89">
-        <v>-35.89981766</v>
+        <v>-36.45326384000001</v>
       </c>
       <c r="Q89">
-        <v>1.100182340000003</v>
+        <v>0.5467361599999947</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3032145979129232</v>
+        <v>0.3246658144056668</v>
       </c>
       <c r="T89">
-        <v>5.944909882515546</v>
+        <v>6.440319039391843</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07632427657255639</v>
+        <v>0.07545695524786825</v>
       </c>
       <c r="W89">
-        <v>0.2178027355841912</v>
+        <v>0.2180072499525527</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2544142552418547</v>
+        <v>0.2515231841595608</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2308062776869264</v>
+        <v>0.2327062776869264</v>
       </c>
       <c r="C90">
-        <v>-200.3047913436271</v>
+        <v>-204.2661669585242</v>
       </c>
       <c r="D90">
-        <v>64.35920865637293</v>
+        <v>63.7508330414758</v>
       </c>
       <c r="E90">
-        <v>130.264</v>
+        <v>133.617</v>
       </c>
       <c r="F90">
-        <v>295.064</v>
+        <v>298.417</v>
       </c>
       <c r="G90">
         <v>30.4</v>
@@ -8673,37 +8673,37 @@
         <v>17.5</v>
       </c>
       <c r="M90">
-        <v>69.57609120000001</v>
+        <v>70.36672860000002</v>
       </c>
       <c r="N90">
-        <v>-52.07609120000001</v>
+        <v>-52.86672860000002</v>
       </c>
       <c r="O90">
-        <v>-15.62282736</v>
+        <v>-15.86001858</v>
       </c>
       <c r="P90">
-        <v>-36.45326384000001</v>
+        <v>-37.00671002000001</v>
       </c>
       <c r="Q90">
-        <v>0.5467361599999947</v>
+        <v>-0.006710020000014083</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3246658144056668</v>
+        <v>0.3500172520789093</v>
       </c>
       <c r="T90">
-        <v>6.440319039391843</v>
+        <v>7.025802588427466</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07545695524786825</v>
+        <v>0.07460912429002702</v>
       </c>
       <c r="W90">
-        <v>0.2180072499525527</v>
+        <v>0.2182071684924116</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2515231841595608</v>
+        <v>0.2486970809667567</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2327062776869264</v>
+        <v>0.2346062776869264</v>
       </c>
       <c r="C91">
-        <v>-204.2661669585242</v>
+        <v>-208.2161485561448</v>
       </c>
       <c r="D91">
-        <v>63.7508330414758</v>
+        <v>63.15385144385523</v>
       </c>
       <c r="E91">
-        <v>133.617</v>
+        <v>136.97</v>
       </c>
       <c r="F91">
-        <v>298.417</v>
+        <v>301.77</v>
       </c>
       <c r="G91">
         <v>30.4</v>
@@ -8755,37 +8755,37 @@
         <v>17.5</v>
       </c>
       <c r="M91">
-        <v>70.36672860000002</v>
+        <v>71.15736600000001</v>
       </c>
       <c r="N91">
-        <v>-52.86672860000002</v>
+        <v>-53.65736600000001</v>
       </c>
       <c r="O91">
-        <v>-15.86001858</v>
+        <v>-16.0972098</v>
       </c>
       <c r="P91">
-        <v>-37.00671002000001</v>
+        <v>-37.56015620000001</v>
       </c>
       <c r="Q91">
-        <v>-0.006710020000014083</v>
+        <v>-0.5601562000000087</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3500172520789093</v>
+        <v>0.3804389772868002</v>
       </c>
       <c r="T91">
-        <v>7.025802588427466</v>
+        <v>7.728382847270212</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07460912429002702</v>
+        <v>0.07378013402013783</v>
       </c>
       <c r="W91">
-        <v>0.2182071684924116</v>
+        <v>0.2184026443980515</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2486970809667567</v>
+        <v>0.2459337800671261</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2346062776869264</v>
+        <v>0.2365062776869264</v>
       </c>
       <c r="C92">
-        <v>-208.2161485561448</v>
+        <v>-212.1550532576844</v>
       </c>
       <c r="D92">
-        <v>63.15385144385523</v>
+        <v>62.56794674231565</v>
       </c>
       <c r="E92">
-        <v>136.97</v>
+        <v>140.323</v>
       </c>
       <c r="F92">
-        <v>301.77</v>
+        <v>305.123</v>
       </c>
       <c r="G92">
         <v>30.4</v>
@@ -8837,37 +8837,37 @@
         <v>17.5</v>
       </c>
       <c r="M92">
-        <v>71.15736600000001</v>
+        <v>71.94800340000002</v>
       </c>
       <c r="N92">
-        <v>-53.65736600000001</v>
+        <v>-54.44800340000002</v>
       </c>
       <c r="O92">
-        <v>-16.0972098</v>
+        <v>-16.33440102</v>
       </c>
       <c r="P92">
-        <v>-37.56015620000001</v>
+        <v>-38.11360238000002</v>
       </c>
       <c r="Q92">
-        <v>-0.5601562000000087</v>
+        <v>-1.113602380000017</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3804389772868002</v>
+        <v>0.4176210858742224</v>
       </c>
       <c r="T92">
-        <v>7.728382847270212</v>
+        <v>8.587092052522458</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07378013402013783</v>
+        <v>0.07296936331661982</v>
       </c>
       <c r="W92">
-        <v>0.2184026443980515</v>
+        <v>0.2185938241299411</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2459337800671261</v>
+        <v>0.2432312110553995</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2365062776869264</v>
+        <v>0.2384062776869263</v>
       </c>
       <c r="C93">
-        <v>-212.1550532576844</v>
+        <v>-216.08318652425</v>
       </c>
       <c r="D93">
-        <v>62.56794674231565</v>
+        <v>61.99281347574999</v>
       </c>
       <c r="E93">
-        <v>140.323</v>
+        <v>143.676</v>
       </c>
       <c r="F93">
-        <v>305.123</v>
+        <v>308.476</v>
       </c>
       <c r="G93">
         <v>30.4</v>
@@ -8919,37 +8919,37 @@
         <v>17.5</v>
       </c>
       <c r="M93">
-        <v>71.94800340000002</v>
+        <v>72.7386408</v>
       </c>
       <c r="N93">
-        <v>-54.44800340000002</v>
+        <v>-55.2386408</v>
       </c>
       <c r="O93">
-        <v>-16.33440102</v>
+        <v>-16.57159224</v>
       </c>
       <c r="P93">
-        <v>-38.11360238000002</v>
+        <v>-38.66704856</v>
       </c>
       <c r="Q93">
-        <v>-1.113602380000017</v>
+        <v>-1.667048559999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4176210858742224</v>
+        <v>0.4640987216085004</v>
       </c>
       <c r="T93">
-        <v>8.587092052522458</v>
+        <v>9.660478559087769</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07296936331661982</v>
+        <v>0.07217621806317832</v>
       </c>
       <c r="W93">
-        <v>0.2185938241299411</v>
+        <v>0.2187808477807026</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2432312110553995</v>
+        <v>0.2405873935439278</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2384062776869263</v>
+        <v>0.2403062776869264</v>
       </c>
       <c r="C94">
-        <v>-216.08318652425</v>
+        <v>-220.0008426878849</v>
       </c>
       <c r="D94">
-        <v>61.99281347574999</v>
+        <v>61.42815731211509</v>
       </c>
       <c r="E94">
-        <v>143.676</v>
+        <v>147.029</v>
       </c>
       <c r="F94">
-        <v>308.476</v>
+        <v>311.829</v>
       </c>
       <c r="G94">
         <v>30.4</v>
@@ -9001,37 +9001,37 @@
         <v>17.5</v>
       </c>
       <c r="M94">
-        <v>72.7386408</v>
+        <v>73.52927820000001</v>
       </c>
       <c r="N94">
-        <v>-55.2386408</v>
+        <v>-56.02927820000001</v>
       </c>
       <c r="O94">
-        <v>-16.57159224</v>
+        <v>-16.80878346</v>
       </c>
       <c r="P94">
-        <v>-38.66704856</v>
+        <v>-39.22049474000001</v>
       </c>
       <c r="Q94">
-        <v>-1.667048559999998</v>
+        <v>-2.220494740000007</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4640987216085004</v>
+        <v>0.5238556818382862</v>
       </c>
       <c r="T94">
-        <v>9.660478559087769</v>
+        <v>11.04054692467174</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07217621806317832</v>
+        <v>0.07140012969690758</v>
       </c>
       <c r="W94">
-        <v>0.2187808477807026</v>
+        <v>0.2189638494174692</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2405873935439278</v>
+        <v>0.2380004323230253</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2403062776869264</v>
+        <v>0.2422062776869263</v>
       </c>
       <c r="C95">
-        <v>-220.0008426878849</v>
+        <v>-223.9083054538339</v>
       </c>
       <c r="D95">
-        <v>61.42815731211509</v>
+        <v>60.87369454616617</v>
       </c>
       <c r="E95">
-        <v>147.029</v>
+        <v>150.382</v>
       </c>
       <c r="F95">
-        <v>311.829</v>
+        <v>315.182</v>
       </c>
       <c r="G95">
         <v>30.4</v>
@@ -9083,37 +9083,37 @@
         <v>17.5</v>
       </c>
       <c r="M95">
-        <v>73.52927820000001</v>
+        <v>74.3199156</v>
       </c>
       <c r="N95">
-        <v>-56.02927820000001</v>
+        <v>-56.8199156</v>
       </c>
       <c r="O95">
-        <v>-16.80878346</v>
+        <v>-17.04597468</v>
       </c>
       <c r="P95">
-        <v>-39.22049474000001</v>
+        <v>-39.77394092</v>
       </c>
       <c r="Q95">
-        <v>-2.220494740000007</v>
+        <v>-2.773940920000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5238556818382862</v>
+        <v>0.603531628811334</v>
       </c>
       <c r="T95">
-        <v>11.04054692467174</v>
+        <v>12.8806380787837</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07140012969690758</v>
+        <v>0.07064055384906814</v>
       </c>
       <c r="W95">
-        <v>0.2189638494174692</v>
+        <v>0.2191429574023897</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2380004323230253</v>
+        <v>0.2354685128302272</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2422062776869263</v>
+        <v>0.2441062776869264</v>
       </c>
       <c r="C96">
-        <v>-223.9083054538339</v>
+        <v>-227.8058483758512</v>
       </c>
       <c r="D96">
-        <v>60.87369454616617</v>
+        <v>60.32915162414885</v>
       </c>
       <c r="E96">
-        <v>150.382</v>
+        <v>153.735</v>
       </c>
       <c r="F96">
-        <v>315.182</v>
+        <v>318.535</v>
       </c>
       <c r="G96">
         <v>30.4</v>
@@ -9165,37 +9165,37 @@
         <v>17.5</v>
       </c>
       <c r="M96">
-        <v>74.3199156</v>
+        <v>75.11055300000001</v>
       </c>
       <c r="N96">
-        <v>-56.8199156</v>
+        <v>-57.61055300000001</v>
       </c>
       <c r="O96">
-        <v>-17.04597468</v>
+        <v>-17.2831659</v>
       </c>
       <c r="P96">
-        <v>-39.77394092</v>
+        <v>-40.32738710000001</v>
       </c>
       <c r="Q96">
-        <v>-2.773940920000001</v>
+        <v>-3.32738710000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.603531628811334</v>
+        <v>0.7150779545736012</v>
       </c>
       <c r="T96">
-        <v>12.8806380787837</v>
+        <v>15.45676569454045</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07064055384906814</v>
+        <v>0.06989696907170953</v>
       </c>
       <c r="W96">
-        <v>0.2191429574023897</v>
+        <v>0.2193182946928909</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2354685128302272</v>
+        <v>0.2329898969056984</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2441062776869264</v>
+        <v>0.2460062776869264</v>
       </c>
       <c r="C97">
-        <v>-227.8058483758512</v>
+        <v>-231.6937353062236</v>
       </c>
       <c r="D97">
-        <v>60.32915162414885</v>
+        <v>59.79426469377648</v>
       </c>
       <c r="E97">
-        <v>153.735</v>
+        <v>157.088</v>
       </c>
       <c r="F97">
-        <v>318.535</v>
+        <v>321.888</v>
       </c>
       <c r="G97">
         <v>30.4</v>
@@ -9247,37 +9247,37 @@
         <v>17.5</v>
       </c>
       <c r="M97">
-        <v>75.11055300000001</v>
+        <v>75.9011904</v>
       </c>
       <c r="N97">
-        <v>-57.61055300000001</v>
+        <v>-58.4011904</v>
       </c>
       <c r="O97">
-        <v>-17.2831659</v>
+        <v>-17.52035712</v>
       </c>
       <c r="P97">
-        <v>-40.32738710000001</v>
+        <v>-40.88083328</v>
       </c>
       <c r="Q97">
-        <v>-3.32738710000001</v>
+        <v>-3.880833280000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7150779545736012</v>
+        <v>0.8823974432170019</v>
       </c>
       <c r="T97">
-        <v>15.45676569454045</v>
+        <v>19.32095711817556</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06989696907170953</v>
+        <v>0.06916887564387922</v>
       </c>
       <c r="W97">
-        <v>0.2193182946928909</v>
+        <v>0.2194899791231733</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2329898969056984</v>
+        <v>0.2305629188129308</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2460062776869264</v>
+        <v>0.2479062776869264</v>
       </c>
       <c r="C98">
-        <v>-231.6937353062235</v>
+        <v>-235.5722208220635</v>
       </c>
       <c r="D98">
-        <v>59.79426469377648</v>
+        <v>59.26877917793647</v>
       </c>
       <c r="E98">
-        <v>157.088</v>
+        <v>160.441</v>
       </c>
       <c r="F98">
-        <v>321.888</v>
+        <v>325.241</v>
       </c>
       <c r="G98">
         <v>30.4</v>
@@ -9329,37 +9329,37 @@
         <v>17.5</v>
       </c>
       <c r="M98">
-        <v>75.9011904</v>
+        <v>76.6918278</v>
       </c>
       <c r="N98">
-        <v>-58.4011904</v>
+        <v>-59.1918278</v>
       </c>
       <c r="O98">
-        <v>-17.52035712</v>
+        <v>-17.75754834</v>
       </c>
       <c r="P98">
-        <v>-40.88083328</v>
+        <v>-41.43427946</v>
       </c>
       <c r="Q98">
-        <v>-3.880833280000004</v>
+        <v>-4.434279459999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8823974432169996</v>
+        <v>1.161263257622666</v>
       </c>
       <c r="T98">
-        <v>19.32095711817551</v>
+        <v>25.76127615756735</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06916887564387922</v>
+        <v>0.0684557944516743</v>
       </c>
       <c r="W98">
-        <v>0.2194899791231733</v>
+        <v>0.2196581236682952</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2305629188129308</v>
+        <v>0.228185981505581</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2479062776869264</v>
+        <v>0.2498062776869264</v>
       </c>
       <c r="C99">
-        <v>-235.5722208220635</v>
+        <v>-239.4415506293206</v>
       </c>
       <c r="D99">
-        <v>59.26877917793647</v>
+        <v>58.7524493706794</v>
       </c>
       <c r="E99">
-        <v>160.441</v>
+        <v>163.794</v>
       </c>
       <c r="F99">
-        <v>325.241</v>
+        <v>328.594</v>
       </c>
       <c r="G99">
         <v>30.4</v>
@@ -9411,37 +9411,37 @@
         <v>17.5</v>
       </c>
       <c r="M99">
-        <v>76.6918278</v>
+        <v>77.48246520000001</v>
       </c>
       <c r="N99">
-        <v>-59.1918278</v>
+        <v>-59.98246520000001</v>
       </c>
       <c r="O99">
-        <v>-17.75754834</v>
+        <v>-17.99473956</v>
       </c>
       <c r="P99">
-        <v>-41.43427946</v>
+        <v>-41.98772564000001</v>
       </c>
       <c r="Q99">
-        <v>-4.434279459999999</v>
+        <v>-4.987725640000008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.161263257622666</v>
+        <v>1.718994886433999</v>
       </c>
       <c r="T99">
-        <v>25.76127615756735</v>
+        <v>38.64191423635103</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0684557944516743</v>
+        <v>0.06775726593686128</v>
       </c>
       <c r="W99">
-        <v>0.2196581236682952</v>
+        <v>0.2198228366920881</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.228185981505581</v>
+        <v>0.2258575531228709</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2498062776869264</v>
+        <v>0.2517062776869264</v>
       </c>
       <c r="C100">
-        <v>-239.4415506293206</v>
+        <v>-243.3019619458569</v>
       </c>
       <c r="D100">
-        <v>58.7524493706794</v>
+        <v>58.24503805414313</v>
       </c>
       <c r="E100">
-        <v>163.794</v>
+        <v>167.147</v>
       </c>
       <c r="F100">
-        <v>328.594</v>
+        <v>331.947</v>
       </c>
       <c r="G100">
         <v>30.4</v>
@@ -9493,37 +9493,37 @@
         <v>17.5</v>
       </c>
       <c r="M100">
-        <v>77.48246520000001</v>
+        <v>78.2731026</v>
       </c>
       <c r="N100">
-        <v>-59.98246520000001</v>
+        <v>-60.7731026</v>
       </c>
       <c r="O100">
-        <v>-17.99473956</v>
+        <v>-18.23193078</v>
       </c>
       <c r="P100">
-        <v>-41.98772564000001</v>
+        <v>-42.54117182</v>
       </c>
       <c r="Q100">
-        <v>-4.987725640000008</v>
+        <v>-5.541171820000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.718994886433999</v>
+        <v>3.392189772867999</v>
       </c>
       <c r="T100">
-        <v>38.64191423635103</v>
+        <v>77.28382847270206</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06775726593686128</v>
+        <v>0.06707284910921621</v>
       </c>
       <c r="W100">
-        <v>0.2198228366920881</v>
+        <v>0.2199842221800468</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2258575531228709</v>
+        <v>0.2235761636973874</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2517062776869264</v>
-      </c>
-      <c r="C101">
-        <v>-243.3019619458569</v>
-      </c>
-      <c r="D101">
-        <v>58.24503805414313</v>
-      </c>
-      <c r="E101">
-        <v>167.147</v>
-      </c>
-      <c r="F101">
-        <v>331.947</v>
-      </c>
-      <c r="G101">
-        <v>30.4</v>
-      </c>
-      <c r="H101">
-        <v>170.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>54.5</v>
-      </c>
-      <c r="K101">
-        <v>37</v>
-      </c>
-      <c r="L101">
-        <v>17.5</v>
-      </c>
-      <c r="M101">
-        <v>78.2731026</v>
-      </c>
-      <c r="N101">
-        <v>-60.7731026</v>
-      </c>
-      <c r="O101">
-        <v>-18.23193078</v>
-      </c>
-      <c r="P101">
-        <v>-42.54117182</v>
-      </c>
-      <c r="Q101">
-        <v>-5.541171820000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.392189772867999</v>
-      </c>
-      <c r="T101">
-        <v>77.28382847270206</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06707284910921621</v>
-      </c>
-      <c r="W101">
-        <v>0.2199842221800468</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2235761636973874</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
